--- a/divFME/ages/nya_ages/TEST_lev1.xlsx
+++ b/divFME/ages/nya_ages/TEST_lev1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\kix\divFME\ages\nya_ages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E4AE29-0ABC-4F36-9D44-376C3F88768F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADAE653-7260-433B-803E-F7891B0AA427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="leverans" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1233,7 +1230,7 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1"/>
@@ -1246,14 +1243,10 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="5" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="8" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="7" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1265,7 +1258,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
@@ -1299,14 +1292,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="9" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="7" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="10">
@@ -1341,9 +1333,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-tema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1381,7 +1373,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1487,7 +1479,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1629,7 +1621,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1637,7 +1629,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAA8AF0D-1C88-4730-B86A-A995F09E08EC}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y227"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1645,90 +1636,90 @@
     <col min="2" max="3" width="16.5703125" customWidth="1"/>
     <col min="4" max="4" width="25.7109375" customWidth="1"/>
     <col min="5" max="5" width="27.7109375" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" style="43" customWidth="1"/>
-    <col min="7" max="8" width="21.7109375" style="17" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" style="38" customWidth="1"/>
+    <col min="7" max="8" width="21.7109375" style="7" customWidth="1"/>
     <col min="9" max="18" width="21.7109375" customWidth="1"/>
-    <col min="19" max="19" width="23.28515625" style="36" customWidth="1"/>
+    <col min="19" max="19" width="23.28515625" style="32" customWidth="1"/>
     <col min="20" max="20" width="20.7109375" customWidth="1"/>
-    <col min="21" max="21" width="20.7109375" style="22" customWidth="1"/>
+    <col min="21" max="21" width="20.7109375" style="18" customWidth="1"/>
     <col min="22" max="22" width="29.42578125" customWidth="1"/>
     <col min="23" max="25" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="33" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:25" s="29" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="J1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="27" t="s">
+      <c r="L1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="28" t="s">
+      <c r="M1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="28" t="s">
+      <c r="N1" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="O1" s="28" t="s">
+      <c r="O1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="29" t="s">
+      <c r="P1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="29" t="s">
+      <c r="Q1" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="R1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="T1" s="30" t="s">
+      <c r="T1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="U1" s="31" t="s">
+      <c r="U1" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="V1" s="32" t="s">
+      <c r="V1" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="W1" s="32" t="s">
+      <c r="W1" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="X1" s="32" t="s">
+      <c r="X1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="Y1" s="32" t="s">
+      <c r="Y1" s="28" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1743,15 +1734,17 @@
         <v>13</v>
       </c>
       <c r="E2" s="1"/>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="2">
         <v>3006</v>
       </c>
-      <c r="J2" s="2"/>
+      <c r="J2" s="2">
+        <v>3006</v>
+      </c>
       <c r="K2" s="2" t="s">
         <v>12</v>
       </c>
@@ -1766,13 +1759,13 @@
       <c r="R2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="35"/>
+      <c r="S2" s="31"/>
       <c r="T2" s="6"/>
-      <c r="U2" s="19"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="23"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="19"/>
+      <c r="W2" s="19"/>
+      <c r="X2" s="19"/>
+      <c r="Y2" s="19"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -1784,15 +1777,17 @@
       <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="34" t="s">
         <v>333</v>
       </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="2">
         <v>3006</v>
       </c>
-      <c r="J3" s="2"/>
+      <c r="J3" s="2">
+        <v>3006</v>
+      </c>
       <c r="K3" s="2" t="s">
         <v>12</v>
       </c>
@@ -1807,13 +1802,13 @@
       <c r="R3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S3" s="35"/>
+      <c r="S3" s="31"/>
       <c r="T3" s="6"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="23"/>
-      <c r="W3" s="23"/>
-      <c r="X3" s="23"/>
-      <c r="Y3" s="23"/>
+      <c r="U3" s="15"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -1825,15 +1820,17 @@
       <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
       <c r="I4" s="2">
         <v>3006</v>
       </c>
-      <c r="J4" s="2"/>
+      <c r="J4" s="2">
+        <v>3006</v>
+      </c>
       <c r="K4" s="2" t="s">
         <v>12</v>
       </c>
@@ -1848,15 +1845,15 @@
       <c r="R4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S4" s="35"/>
+      <c r="S4" s="31"/>
       <c r="T4" s="6"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="23"/>
-      <c r="W4" s="23"/>
-      <c r="X4" s="23"/>
-      <c r="Y4" s="23"/>
-    </row>
-    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+      <c r="U4" s="15"/>
+      <c r="V4" s="19"/>
+      <c r="W4" s="19"/>
+      <c r="X4" s="19"/>
+      <c r="Y4" s="19"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>93</v>
       </c>
@@ -1866,11 +1863,11 @@
       <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="F5" s="34" t="s">
         <v>265</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
       <c r="I5" s="2">
         <v>3006</v>
       </c>
@@ -1889,15 +1886,15 @@
       <c r="R5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="S5" s="35" t="s">
+      <c r="S5" s="31" t="s">
         <v>83</v>
       </c>
       <c r="T5" s="6"/>
-      <c r="U5" s="19"/>
-      <c r="V5" s="23"/>
-      <c r="W5" s="23"/>
-      <c r="X5" s="23"/>
-      <c r="Y5" s="23"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="19"/>
+      <c r="W5" s="19"/>
+      <c r="X5" s="19"/>
+      <c r="Y5" s="19"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1909,15 +1906,17 @@
       <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="34" t="s">
         <v>221</v>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
       <c r="I6" s="2">
         <v>3006</v>
       </c>
-      <c r="J6" s="2"/>
+      <c r="J6" s="2">
+        <v>3006</v>
+      </c>
       <c r="K6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1932,13 +1931,13 @@
       <c r="R6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S6" s="35"/>
+      <c r="S6" s="31"/>
       <c r="T6" s="6"/>
-      <c r="U6" s="19"/>
-      <c r="V6" s="23"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="23"/>
-      <c r="Y6" s="23"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1950,15 +1949,17 @@
       <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="34" t="s">
         <v>222</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
       <c r="I7" s="2">
         <v>3006</v>
       </c>
-      <c r="J7" s="2"/>
+      <c r="J7" s="2">
+        <v>3006</v>
+      </c>
       <c r="K7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1973,13 +1974,13 @@
       <c r="R7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S7" s="35"/>
+      <c r="S7" s="31"/>
       <c r="T7" s="6"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="23"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="23"/>
-      <c r="Y7" s="23"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1991,11 +1992,11 @@
       <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="F8" s="34" t="s">
         <v>223</v>
       </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
       <c r="I8" s="2">
         <v>3006</v>
       </c>
@@ -2016,13 +2017,13 @@
       <c r="R8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S8" s="35"/>
+      <c r="S8" s="31"/>
       <c r="T8" s="6"/>
-      <c r="U8" s="19"/>
-      <c r="V8" s="23"/>
-      <c r="W8" s="23"/>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="23"/>
+      <c r="U8" s="15"/>
+      <c r="V8" s="19"/>
+      <c r="W8" s="19"/>
+      <c r="X8" s="19"/>
+      <c r="Y8" s="19"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -2034,15 +2035,17 @@
       <c r="C9" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="38" t="s">
+      <c r="F9" s="34" t="s">
         <v>224</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
       <c r="I9" s="2">
         <v>3006</v>
       </c>
-      <c r="J9" s="2"/>
+      <c r="J9" s="2">
+        <v>3006</v>
+      </c>
       <c r="K9" s="2" t="s">
         <v>12</v>
       </c>
@@ -2057,13 +2060,13 @@
       <c r="R9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S9" s="35"/>
+      <c r="S9" s="31"/>
       <c r="T9" s="6"/>
-      <c r="U9" s="19"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="23"/>
-      <c r="Y9" s="23"/>
+      <c r="U9" s="15"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="19"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -2075,15 +2078,17 @@
       <c r="C10" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="34" t="s">
         <v>225</v>
       </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
       <c r="I10" s="2">
         <v>3006</v>
       </c>
-      <c r="J10" s="2"/>
+      <c r="J10" s="2">
+        <v>3006</v>
+      </c>
       <c r="K10" s="2" t="s">
         <v>12</v>
       </c>
@@ -2098,13 +2103,13 @@
       <c r="R10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S10" s="35"/>
+      <c r="S10" s="31"/>
       <c r="T10" s="6"/>
-      <c r="U10" s="19"/>
-      <c r="V10" s="23"/>
-      <c r="W10" s="23"/>
-      <c r="X10" s="23"/>
-      <c r="Y10" s="23"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="19"/>
+      <c r="Y10" s="19"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -2116,15 +2121,17 @@
       <c r="C11" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="38" t="s">
+      <c r="F11" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
       <c r="I11" s="2">
         <v>3006</v>
       </c>
-      <c r="J11" s="2"/>
+      <c r="J11" s="2">
+        <v>3006</v>
+      </c>
       <c r="K11" s="2" t="s">
         <v>12</v>
       </c>
@@ -2139,13 +2146,13 @@
       <c r="R11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S11" s="35"/>
+      <c r="S11" s="31"/>
       <c r="T11" s="6"/>
-      <c r="U11" s="19"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="23"/>
-      <c r="X11" s="23"/>
-      <c r="Y11" s="23"/>
+      <c r="U11" s="15"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="19"/>
+      <c r="Y11" s="19"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -2157,15 +2164,17 @@
       <c r="C12" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
       <c r="I12" s="2">
         <v>3006</v>
       </c>
-      <c r="J12" s="2"/>
+      <c r="J12" s="2">
+        <v>3006</v>
+      </c>
       <c r="K12" s="2" t="s">
         <v>12</v>
       </c>
@@ -2180,13 +2189,13 @@
       <c r="R12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S12" s="35"/>
+      <c r="S12" s="31"/>
       <c r="T12" s="6"/>
-      <c r="U12" s="19"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="23"/>
-      <c r="X12" s="23"/>
-      <c r="Y12" s="23"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="19"/>
+      <c r="Y12" s="19"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -2198,15 +2207,17 @@
       <c r="C13" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="38" t="s">
+      <c r="F13" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
       <c r="I13" s="2">
         <v>3006</v>
       </c>
-      <c r="J13" s="2"/>
+      <c r="J13" s="2">
+        <v>3006</v>
+      </c>
       <c r="K13" s="2" t="s">
         <v>12</v>
       </c>
@@ -2221,13 +2232,13 @@
       <c r="R13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S13" s="35"/>
+      <c r="S13" s="31"/>
       <c r="T13" s="6"/>
-      <c r="U13" s="19"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="23"/>
+      <c r="U13" s="15"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="19"/>
+      <c r="Y13" s="19"/>
     </row>
     <row r="14" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -2239,15 +2250,17 @@
       <c r="C14" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="F14" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
       <c r="I14" s="2">
         <v>3006</v>
       </c>
-      <c r="J14" s="2"/>
+      <c r="J14" s="2">
+        <v>3006</v>
+      </c>
       <c r="K14" s="2" t="s">
         <v>12</v>
       </c>
@@ -2262,13 +2275,13 @@
       <c r="R14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S14" s="35"/>
+      <c r="S14" s="31"/>
       <c r="T14" s="6"/>
-      <c r="U14" s="19"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
+      <c r="U14" s="15"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="19"/>
+      <c r="Y14" s="19"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -2280,15 +2293,17 @@
       <c r="C15" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="38" t="s">
+      <c r="F15" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
       <c r="I15" s="2">
         <v>3006</v>
       </c>
-      <c r="J15" s="2"/>
+      <c r="J15" s="2">
+        <v>3006</v>
+      </c>
       <c r="K15" s="2" t="s">
         <v>12</v>
       </c>
@@ -2303,13 +2318,13 @@
       <c r="R15" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S15" s="35"/>
+      <c r="S15" s="31"/>
       <c r="T15" s="6"/>
-      <c r="U15" s="19"/>
-      <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="23"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="19"/>
+      <c r="X15" s="19"/>
+      <c r="Y15" s="19"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -2321,15 +2336,17 @@
       <c r="C16" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="38" t="s">
+      <c r="F16" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
       <c r="I16" s="2">
         <v>3006</v>
       </c>
-      <c r="J16" s="2"/>
+      <c r="J16" s="2">
+        <v>3006</v>
+      </c>
       <c r="K16" s="2" t="s">
         <v>12</v>
       </c>
@@ -2344,13 +2361,13 @@
       <c r="R16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S16" s="35"/>
+      <c r="S16" s="31"/>
       <c r="T16" s="6"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="23"/>
-      <c r="W16" s="23"/>
-      <c r="X16" s="23"/>
-      <c r="Y16" s="23"/>
+      <c r="U16" s="15"/>
+      <c r="V16" s="19"/>
+      <c r="W16" s="19"/>
+      <c r="X16" s="19"/>
+      <c r="Y16" s="19"/>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -2362,15 +2379,17 @@
       <c r="C17" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="38" t="s">
+      <c r="F17" s="34" t="s">
         <v>232</v>
       </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
       <c r="I17" s="2">
         <v>3006</v>
       </c>
-      <c r="J17" s="2"/>
+      <c r="J17" s="2">
+        <v>3006</v>
+      </c>
       <c r="K17" s="2" t="s">
         <v>12</v>
       </c>
@@ -2385,13 +2404,13 @@
       <c r="R17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S17" s="35"/>
+      <c r="S17" s="31"/>
       <c r="T17" s="6"/>
-      <c r="U17" s="19"/>
-      <c r="V17" s="23"/>
-      <c r="W17" s="23"/>
-      <c r="X17" s="23"/>
-      <c r="Y17" s="23"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="19"/>
+      <c r="W17" s="19"/>
+      <c r="X17" s="19"/>
+      <c r="Y17" s="19"/>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -2403,16 +2422,17 @@
       <c r="C18" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="34" t="s">
         <v>233</v>
       </c>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
       <c r="I18" s="2">
         <v>3006</v>
       </c>
-      <c r="J18" s="2"/>
+      <c r="J18" s="2">
+        <v>3006</v>
+      </c>
       <c r="K18" s="2" t="s">
         <v>12</v>
       </c>
@@ -2427,13 +2447,13 @@
       <c r="R18" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S18" s="35"/>
+      <c r="S18" s="31"/>
       <c r="T18" s="6"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="23"/>
-      <c r="W18" s="23"/>
-      <c r="X18" s="23"/>
-      <c r="Y18" s="23"/>
+      <c r="U18" s="15"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="19"/>
+      <c r="X18" s="19"/>
+      <c r="Y18" s="19"/>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -2445,16 +2465,17 @@
       <c r="C19" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="12"/>
-      <c r="F19" s="38" t="s">
+      <c r="F19" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
       <c r="I19" s="2">
         <v>3006</v>
       </c>
-      <c r="J19" s="2"/>
+      <c r="J19" s="2">
+        <v>3006</v>
+      </c>
       <c r="K19" s="2" t="s">
         <v>12</v>
       </c>
@@ -2469,13 +2490,13 @@
       <c r="R19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S19" s="35"/>
+      <c r="S19" s="31"/>
       <c r="T19" s="6"/>
-      <c r="U19" s="19"/>
-      <c r="V19" s="23"/>
-      <c r="W19" s="23"/>
-      <c r="X19" s="23"/>
-      <c r="Y19" s="23"/>
+      <c r="U19" s="15"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="19"/>
+      <c r="X19" s="19"/>
+      <c r="Y19" s="19"/>
     </row>
     <row r="20" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -2487,16 +2508,17 @@
       <c r="C20" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="F20" s="38" t="s">
+      <c r="F20" s="34" t="s">
         <v>235</v>
       </c>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
       <c r="I20" s="2">
         <v>3006</v>
       </c>
-      <c r="J20" s="2"/>
+      <c r="J20" s="2">
+        <v>3006</v>
+      </c>
       <c r="K20" s="2" t="s">
         <v>12</v>
       </c>
@@ -2511,13 +2533,13 @@
       <c r="R20" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S20" s="35"/>
+      <c r="S20" s="31"/>
       <c r="T20" s="6"/>
-      <c r="U20" s="19"/>
-      <c r="V20" s="23"/>
-      <c r="W20" s="23"/>
-      <c r="X20" s="23"/>
-      <c r="Y20" s="23"/>
+      <c r="U20" s="15"/>
+      <c r="V20" s="19"/>
+      <c r="W20" s="19"/>
+      <c r="X20" s="19"/>
+      <c r="Y20" s="19"/>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -2529,16 +2551,17 @@
       <c r="C21" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="F21" s="38" t="s">
+      <c r="F21" s="34" t="s">
         <v>236</v>
       </c>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
       <c r="I21" s="2">
         <v>3006</v>
       </c>
-      <c r="J21" s="2"/>
+      <c r="J21" s="2">
+        <v>3006</v>
+      </c>
       <c r="K21" s="2" t="s">
         <v>12</v>
       </c>
@@ -2553,13 +2576,13 @@
       <c r="R21" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S21" s="35"/>
+      <c r="S21" s="31"/>
       <c r="T21" s="6"/>
-      <c r="U21" s="19"/>
-      <c r="V21" s="23"/>
-      <c r="W21" s="23"/>
-      <c r="X21" s="23"/>
-      <c r="Y21" s="23"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="19"/>
+      <c r="W21" s="19"/>
+      <c r="X21" s="19"/>
+      <c r="Y21" s="19"/>
     </row>
     <row r="22" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
@@ -2571,16 +2594,17 @@
       <c r="C22" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="F22" s="38" t="s">
+      <c r="F22" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
       <c r="I22" s="2">
         <v>3006</v>
       </c>
-      <c r="J22" s="2"/>
+      <c r="J22" s="2">
+        <v>3006</v>
+      </c>
       <c r="K22" s="2" t="s">
         <v>12</v>
       </c>
@@ -2595,13 +2619,13 @@
       <c r="R22" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S22" s="35"/>
+      <c r="S22" s="31"/>
       <c r="T22" s="6"/>
-      <c r="U22" s="19"/>
-      <c r="V22" s="23"/>
-      <c r="W22" s="23"/>
-      <c r="X22" s="23"/>
-      <c r="Y22" s="23"/>
+      <c r="U22" s="15"/>
+      <c r="V22" s="19"/>
+      <c r="W22" s="19"/>
+      <c r="X22" s="19"/>
+      <c r="Y22" s="19"/>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -2613,17 +2637,18 @@
       <c r="C23" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="12"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="38" t="s">
+      <c r="F23" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
       <c r="I23" s="2">
         <v>3006</v>
       </c>
-      <c r="J23" s="2"/>
+      <c r="J23" s="2">
+        <v>3006</v>
+      </c>
       <c r="K23" s="2" t="s">
         <v>12</v>
       </c>
@@ -2638,13 +2663,13 @@
       <c r="R23" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S23" s="35"/>
+      <c r="S23" s="31"/>
       <c r="T23" s="6"/>
-      <c r="U23" s="19"/>
-      <c r="V23" s="23"/>
-      <c r="W23" s="23"/>
-      <c r="X23" s="23"/>
-      <c r="Y23" s="23"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="19"/>
+      <c r="W23" s="19"/>
+      <c r="X23" s="19"/>
+      <c r="Y23" s="19"/>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -2656,16 +2681,17 @@
       <c r="C24" t="s">
         <v>13</v>
       </c>
-      <c r="D24" s="12"/>
-      <c r="F24" s="38" t="s">
+      <c r="F24" s="34" t="s">
         <v>239</v>
       </c>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
       <c r="I24" s="2">
         <v>3006</v>
       </c>
-      <c r="J24" s="2"/>
+      <c r="J24" s="2">
+        <v>3006</v>
+      </c>
       <c r="K24" s="2" t="s">
         <v>12</v>
       </c>
@@ -2680,13 +2706,13 @@
       <c r="R24" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S24" s="35"/>
+      <c r="S24" s="31"/>
       <c r="T24" s="6"/>
-      <c r="U24" s="19"/>
-      <c r="V24" s="23"/>
-      <c r="W24" s="23"/>
-      <c r="X24" s="23"/>
-      <c r="Y24" s="23"/>
+      <c r="U24" s="15"/>
+      <c r="V24" s="19"/>
+      <c r="W24" s="19"/>
+      <c r="X24" s="19"/>
+      <c r="Y24" s="19"/>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -2698,16 +2724,17 @@
       <c r="C25" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="12"/>
-      <c r="F25" s="38" t="s">
+      <c r="F25" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
       <c r="I25" s="2">
         <v>3006</v>
       </c>
-      <c r="J25" s="2"/>
+      <c r="J25" s="2">
+        <v>3006</v>
+      </c>
       <c r="K25" s="2" t="s">
         <v>12</v>
       </c>
@@ -2722,13 +2749,13 @@
       <c r="R25" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S25" s="35"/>
+      <c r="S25" s="31"/>
       <c r="T25" s="6"/>
-      <c r="U25" s="19"/>
-      <c r="V25" s="23"/>
-      <c r="W25" s="23"/>
-      <c r="X25" s="23"/>
-      <c r="Y25" s="23"/>
+      <c r="U25" s="15"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="19"/>
+      <c r="Y25" s="19"/>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -2740,16 +2767,17 @@
       <c r="C26" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="12"/>
-      <c r="F26" s="38" t="s">
+      <c r="F26" s="34" t="s">
         <v>241</v>
       </c>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
       <c r="I26" s="2">
         <v>3006</v>
       </c>
-      <c r="J26" s="2"/>
+      <c r="J26" s="2">
+        <v>3006</v>
+      </c>
       <c r="K26" s="2" t="s">
         <v>12</v>
       </c>
@@ -2764,13 +2792,13 @@
       <c r="R26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S26" s="35"/>
+      <c r="S26" s="31"/>
       <c r="T26" s="6"/>
-      <c r="U26" s="19"/>
-      <c r="V26" s="23"/>
-      <c r="W26" s="23"/>
-      <c r="X26" s="23"/>
-      <c r="Y26" s="23"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="19"/>
+      <c r="Y26" s="19"/>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -2782,16 +2810,17 @@
       <c r="C27" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="12"/>
-      <c r="F27" s="38" t="s">
+      <c r="F27" s="34" t="s">
         <v>242</v>
       </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
       <c r="I27" s="2">
         <v>3006</v>
       </c>
-      <c r="J27" s="2"/>
+      <c r="J27" s="2">
+        <v>3006</v>
+      </c>
       <c r="K27" s="2" t="s">
         <v>12</v>
       </c>
@@ -2806,13 +2835,13 @@
       <c r="R27" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S27" s="35"/>
+      <c r="S27" s="31"/>
       <c r="T27" s="6"/>
-      <c r="U27" s="19"/>
-      <c r="V27" s="23"/>
-      <c r="W27" s="23"/>
-      <c r="X27" s="23"/>
-      <c r="Y27" s="23"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="19"/>
+      <c r="Y27" s="19"/>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -2824,17 +2853,18 @@
       <c r="C28" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="12"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="38" t="s">
+      <c r="F28" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
       <c r="I28" s="2">
         <v>3006</v>
       </c>
-      <c r="J28" s="2"/>
+      <c r="J28" s="2">
+        <v>3006</v>
+      </c>
       <c r="K28" s="2" t="s">
         <v>12</v>
       </c>
@@ -2849,13 +2879,13 @@
       <c r="R28" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S28" s="35"/>
+      <c r="S28" s="31"/>
       <c r="T28" s="6"/>
-      <c r="U28" s="19"/>
-      <c r="V28" s="23"/>
-      <c r="W28" s="23"/>
-      <c r="X28" s="23"/>
-      <c r="Y28" s="23"/>
+      <c r="U28" s="15"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="19"/>
+      <c r="Y28" s="19"/>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -2867,16 +2897,17 @@
       <c r="C29" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="12"/>
-      <c r="F29" s="38" t="s">
+      <c r="F29" s="34" t="s">
         <v>244</v>
       </c>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
       <c r="I29" s="2">
         <v>3006</v>
       </c>
-      <c r="J29" s="2"/>
+      <c r="J29" s="2">
+        <v>3006</v>
+      </c>
       <c r="K29" s="2" t="s">
         <v>12</v>
       </c>
@@ -2891,13 +2922,13 @@
       <c r="R29" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S29" s="35"/>
+      <c r="S29" s="31"/>
       <c r="T29" s="6"/>
-      <c r="U29" s="19"/>
-      <c r="V29" s="23"/>
-      <c r="W29" s="23"/>
-      <c r="X29" s="23"/>
-      <c r="Y29" s="23"/>
+      <c r="U29" s="15"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="19"/>
+      <c r="Y29" s="19"/>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -2909,17 +2940,18 @@
       <c r="C30" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="12"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="38" t="s">
+      <c r="F30" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
       <c r="I30" s="2">
         <v>3006</v>
       </c>
-      <c r="J30" s="2"/>
+      <c r="J30" s="2">
+        <v>3006</v>
+      </c>
       <c r="K30" s="2" t="s">
         <v>12</v>
       </c>
@@ -2934,13 +2966,13 @@
       <c r="R30" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S30" s="35"/>
+      <c r="S30" s="31"/>
       <c r="T30" s="6"/>
-      <c r="U30" s="19"/>
-      <c r="V30" s="23"/>
-      <c r="W30" s="23"/>
-      <c r="X30" s="23"/>
-      <c r="Y30" s="23"/>
+      <c r="U30" s="15"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="19"/>
+      <c r="Y30" s="19"/>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
@@ -2952,16 +2984,17 @@
       <c r="C31" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="12"/>
-      <c r="F31" s="38" t="s">
+      <c r="F31" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
       <c r="I31" s="2">
         <v>3006</v>
       </c>
-      <c r="J31" s="2"/>
+      <c r="J31" s="2">
+        <v>3006</v>
+      </c>
       <c r="K31" s="2" t="s">
         <v>12</v>
       </c>
@@ -2976,13 +3009,13 @@
       <c r="R31" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S31" s="35"/>
+      <c r="S31" s="31"/>
       <c r="T31" s="6"/>
-      <c r="U31" s="19"/>
-      <c r="V31" s="23"/>
-      <c r="W31" s="23"/>
-      <c r="X31" s="23"/>
-      <c r="Y31" s="23"/>
+      <c r="U31" s="15"/>
+      <c r="V31" s="19"/>
+      <c r="W31" s="19"/>
+      <c r="X31" s="19"/>
+      <c r="Y31" s="19"/>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -2994,16 +3027,17 @@
       <c r="C32" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="12"/>
-      <c r="F32" s="38" t="s">
+      <c r="F32" s="34" t="s">
         <v>247</v>
       </c>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
       <c r="I32" s="2">
         <v>3006</v>
       </c>
-      <c r="J32" s="2"/>
+      <c r="J32" s="2">
+        <v>3006</v>
+      </c>
       <c r="K32" s="2" t="s">
         <v>12</v>
       </c>
@@ -3018,13 +3052,13 @@
       <c r="R32" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S32" s="35"/>
+      <c r="S32" s="31"/>
       <c r="T32" s="6"/>
-      <c r="U32" s="19"/>
-      <c r="V32" s="23"/>
-      <c r="W32" s="23"/>
-      <c r="X32" s="23"/>
-      <c r="Y32" s="23"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="19"/>
+      <c r="W32" s="19"/>
+      <c r="X32" s="19"/>
+      <c r="Y32" s="19"/>
     </row>
     <row r="33" spans="1:25" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
@@ -3036,16 +3070,17 @@
       <c r="C33" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="12"/>
-      <c r="F33" s="38" t="s">
+      <c r="F33" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
       <c r="I33" s="2">
         <v>3006</v>
       </c>
-      <c r="J33" s="2"/>
+      <c r="J33" s="2">
+        <v>3006</v>
+      </c>
       <c r="K33" s="2" t="s">
         <v>12</v>
       </c>
@@ -3060,13 +3095,13 @@
       <c r="R33" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S33" s="35"/>
+      <c r="S33" s="31"/>
       <c r="T33" s="6"/>
-      <c r="U33" s="19"/>
-      <c r="V33" s="23"/>
-      <c r="W33" s="23"/>
-      <c r="X33" s="23"/>
-      <c r="Y33" s="23"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="19"/>
+      <c r="W33" s="19"/>
+      <c r="X33" s="19"/>
+      <c r="Y33" s="19"/>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
@@ -3078,16 +3113,17 @@
       <c r="C34" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="12"/>
-      <c r="F34" s="38" t="s">
+      <c r="F34" s="34" t="s">
         <v>232</v>
       </c>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
       <c r="I34" s="2">
         <v>3006</v>
       </c>
-      <c r="J34" s="2"/>
+      <c r="J34" s="2">
+        <v>3006</v>
+      </c>
       <c r="K34" s="2" t="s">
         <v>12</v>
       </c>
@@ -3102,13 +3138,13 @@
       <c r="R34" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S34" s="35"/>
+      <c r="S34" s="31"/>
       <c r="T34" s="6"/>
-      <c r="U34" s="19"/>
-      <c r="V34" s="23"/>
-      <c r="W34" s="23"/>
-      <c r="X34" s="23"/>
-      <c r="Y34" s="23"/>
+      <c r="U34" s="15"/>
+      <c r="V34" s="19"/>
+      <c r="W34" s="19"/>
+      <c r="X34" s="19"/>
+      <c r="Y34" s="19"/>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
@@ -3120,16 +3156,17 @@
       <c r="C35" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="12"/>
-      <c r="F35" s="38" t="s">
+      <c r="F35" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
       <c r="I35" s="2">
         <v>3006</v>
       </c>
-      <c r="J35" s="2"/>
+      <c r="J35" s="2">
+        <v>3006</v>
+      </c>
       <c r="K35" s="2" t="s">
         <v>12</v>
       </c>
@@ -3144,13 +3181,13 @@
       <c r="R35" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S35" s="35"/>
+      <c r="S35" s="31"/>
       <c r="T35" s="6"/>
-      <c r="U35" s="19"/>
-      <c r="V35" s="23"/>
-      <c r="W35" s="23"/>
-      <c r="X35" s="23"/>
-      <c r="Y35" s="23"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="19"/>
+      <c r="W35" s="19"/>
+      <c r="X35" s="19"/>
+      <c r="Y35" s="19"/>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
@@ -3162,17 +3199,18 @@
       <c r="C36" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="12"/>
       <c r="E36" s="1"/>
-      <c r="F36" s="38" t="s">
+      <c r="F36" s="34" t="s">
         <v>250</v>
       </c>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
       <c r="I36" s="2">
         <v>3006</v>
       </c>
-      <c r="J36" s="2"/>
+      <c r="J36" s="2">
+        <v>3006</v>
+      </c>
       <c r="K36" s="2" t="s">
         <v>12</v>
       </c>
@@ -3187,13 +3225,13 @@
       <c r="R36" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S36" s="35"/>
+      <c r="S36" s="31"/>
       <c r="T36" s="6"/>
-      <c r="U36" s="19"/>
-      <c r="V36" s="23"/>
-      <c r="W36" s="23"/>
-      <c r="X36" s="23"/>
-      <c r="Y36" s="23"/>
+      <c r="U36" s="15"/>
+      <c r="V36" s="19"/>
+      <c r="W36" s="19"/>
+      <c r="X36" s="19"/>
+      <c r="Y36" s="19"/>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
@@ -3205,16 +3243,17 @@
       <c r="C37" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="12"/>
-      <c r="F37" s="38" t="s">
+      <c r="F37" s="34" t="s">
         <v>251</v>
       </c>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
       <c r="I37" s="2">
         <v>3006</v>
       </c>
-      <c r="J37" s="2"/>
+      <c r="J37" s="2">
+        <v>3006</v>
+      </c>
       <c r="K37" s="2" t="s">
         <v>12</v>
       </c>
@@ -3229,13 +3268,13 @@
       <c r="R37" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S37" s="35"/>
+      <c r="S37" s="31"/>
       <c r="T37" s="6"/>
-      <c r="U37" s="19"/>
-      <c r="V37" s="23"/>
-      <c r="W37" s="23"/>
-      <c r="X37" s="23"/>
-      <c r="Y37" s="23"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="19"/>
+      <c r="W37" s="19"/>
+      <c r="X37" s="19"/>
+      <c r="Y37" s="19"/>
     </row>
     <row r="38" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
@@ -3247,16 +3286,17 @@
       <c r="C38" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="12"/>
-      <c r="F38" s="38" t="s">
+      <c r="F38" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
       <c r="I38" s="2">
         <v>3006</v>
       </c>
-      <c r="J38" s="2"/>
+      <c r="J38" s="2">
+        <v>3006</v>
+      </c>
       <c r="K38" s="2" t="s">
         <v>12</v>
       </c>
@@ -3271,13 +3311,13 @@
       <c r="R38" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S38" s="35"/>
+      <c r="S38" s="31"/>
       <c r="T38" s="6"/>
-      <c r="U38" s="19"/>
-      <c r="V38" s="23"/>
-      <c r="W38" s="23"/>
-      <c r="X38" s="23"/>
-      <c r="Y38" s="23"/>
+      <c r="U38" s="15"/>
+      <c r="V38" s="19"/>
+      <c r="W38" s="19"/>
+      <c r="X38" s="19"/>
+      <c r="Y38" s="19"/>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
@@ -3289,16 +3329,17 @@
       <c r="C39" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="12"/>
-      <c r="F39" s="38" t="s">
+      <c r="F39" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
       <c r="I39" s="2">
         <v>3006</v>
       </c>
-      <c r="J39" s="2"/>
+      <c r="J39" s="2">
+        <v>3006</v>
+      </c>
       <c r="K39" s="2" t="s">
         <v>12</v>
       </c>
@@ -3313,13 +3354,13 @@
       <c r="R39" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S39" s="35"/>
+      <c r="S39" s="31"/>
       <c r="T39" s="6"/>
-      <c r="U39" s="19"/>
-      <c r="V39" s="23"/>
-      <c r="W39" s="23"/>
-      <c r="X39" s="23"/>
-      <c r="Y39" s="23"/>
+      <c r="U39" s="15"/>
+      <c r="V39" s="19"/>
+      <c r="W39" s="19"/>
+      <c r="X39" s="19"/>
+      <c r="Y39" s="19"/>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
@@ -3331,16 +3372,17 @@
       <c r="C40" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="12"/>
-      <c r="F40" s="38" t="s">
+      <c r="F40" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
       <c r="I40" s="2">
         <v>3006</v>
       </c>
-      <c r="J40" s="2"/>
+      <c r="J40" s="2">
+        <v>3006</v>
+      </c>
       <c r="K40" s="2" t="s">
         <v>12</v>
       </c>
@@ -3355,13 +3397,13 @@
       <c r="R40" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S40" s="35"/>
+      <c r="S40" s="31"/>
       <c r="T40" s="6"/>
-      <c r="U40" s="19"/>
-      <c r="V40" s="23"/>
-      <c r="W40" s="23"/>
-      <c r="X40" s="23"/>
-      <c r="Y40" s="23"/>
+      <c r="U40" s="15"/>
+      <c r="V40" s="19"/>
+      <c r="W40" s="19"/>
+      <c r="X40" s="19"/>
+      <c r="Y40" s="19"/>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
@@ -3373,17 +3415,18 @@
       <c r="C41" t="s">
         <v>13</v>
       </c>
-      <c r="D41" s="12"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="38" t="s">
+      <c r="F41" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
       <c r="I41" s="2">
         <v>3006</v>
       </c>
-      <c r="J41" s="2"/>
+      <c r="J41" s="2">
+        <v>3006</v>
+      </c>
       <c r="K41" s="2" t="s">
         <v>12</v>
       </c>
@@ -3398,13 +3441,13 @@
       <c r="R41" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S41" s="35"/>
+      <c r="S41" s="31"/>
       <c r="T41" s="6"/>
-      <c r="U41" s="19"/>
-      <c r="V41" s="23"/>
-      <c r="W41" s="23"/>
-      <c r="X41" s="23"/>
-      <c r="Y41" s="23"/>
+      <c r="U41" s="15"/>
+      <c r="V41" s="19"/>
+      <c r="W41" s="19"/>
+      <c r="X41" s="19"/>
+      <c r="Y41" s="19"/>
     </row>
     <row r="42" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
@@ -3416,17 +3459,18 @@
       <c r="C42" t="s">
         <v>13</v>
       </c>
-      <c r="D42" s="12"/>
       <c r="E42" s="1"/>
-      <c r="F42" s="38" t="s">
+      <c r="F42" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
       <c r="I42" s="2">
         <v>3006</v>
       </c>
-      <c r="J42" s="2"/>
+      <c r="J42" s="2">
+        <v>3006</v>
+      </c>
       <c r="K42" s="2" t="s">
         <v>12</v>
       </c>
@@ -3441,13 +3485,13 @@
       <c r="R42" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S42" s="35"/>
+      <c r="S42" s="31"/>
       <c r="T42" s="6"/>
-      <c r="U42" s="19"/>
-      <c r="V42" s="23"/>
-      <c r="W42" s="23"/>
-      <c r="X42" s="23"/>
-      <c r="Y42" s="23"/>
+      <c r="U42" s="15"/>
+      <c r="V42" s="19"/>
+      <c r="W42" s="19"/>
+      <c r="X42" s="19"/>
+      <c r="Y42" s="19"/>
     </row>
     <row r="43" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -3459,17 +3503,18 @@
       <c r="C43" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="12"/>
       <c r="E43" s="11"/>
-      <c r="F43" s="38" t="s">
+      <c r="F43" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
       <c r="I43" s="2">
         <v>3006</v>
       </c>
-      <c r="J43" s="2"/>
+      <c r="J43" s="2">
+        <v>3006</v>
+      </c>
       <c r="K43" s="2" t="s">
         <v>12</v>
       </c>
@@ -3484,13 +3529,13 @@
       <c r="R43" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S43" s="35"/>
+      <c r="S43" s="31"/>
       <c r="T43" s="6"/>
-      <c r="U43" s="19"/>
-      <c r="V43" s="23"/>
-      <c r="W43" s="23"/>
-      <c r="X43" s="23"/>
-      <c r="Y43" s="23"/>
+      <c r="U43" s="15"/>
+      <c r="V43" s="19"/>
+      <c r="W43" s="19"/>
+      <c r="X43" s="19"/>
+      <c r="Y43" s="19"/>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -3502,17 +3547,18 @@
       <c r="C44" t="s">
         <v>13</v>
       </c>
-      <c r="D44" s="12"/>
       <c r="E44" s="11"/>
-      <c r="F44" s="38" t="s">
+      <c r="F44" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
       <c r="I44" s="2">
         <v>3006</v>
       </c>
-      <c r="J44" s="2"/>
+      <c r="J44" s="2">
+        <v>3006</v>
+      </c>
       <c r="K44" s="2" t="s">
         <v>12</v>
       </c>
@@ -3527,13 +3573,13 @@
       <c r="R44" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S44" s="35"/>
+      <c r="S44" s="31"/>
       <c r="T44" s="6"/>
-      <c r="U44" s="19"/>
-      <c r="V44" s="23"/>
-      <c r="W44" s="23"/>
-      <c r="X44" s="23"/>
-      <c r="Y44" s="23"/>
+      <c r="U44" s="15"/>
+      <c r="V44" s="19"/>
+      <c r="W44" s="19"/>
+      <c r="X44" s="19"/>
+      <c r="Y44" s="19"/>
     </row>
     <row r="45" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -3545,17 +3591,19 @@
       <c r="C45" t="s">
         <v>13</v>
       </c>
-      <c r="D45" s="12"/>
+      <c r="D45"/>
       <c r="E45"/>
-      <c r="F45" s="38" t="s">
+      <c r="F45" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
       <c r="I45" s="8">
         <v>3006</v>
       </c>
-      <c r="J45" s="8"/>
+      <c r="J45" s="2">
+        <v>3006</v>
+      </c>
       <c r="K45" s="2" t="s">
         <v>12</v>
       </c>
@@ -3570,13 +3618,13 @@
       <c r="R45" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S45" s="35"/>
+      <c r="S45" s="31"/>
       <c r="T45" s="10"/>
-      <c r="U45" s="20"/>
-      <c r="V45" s="23"/>
-      <c r="W45" s="23"/>
-      <c r="X45" s="23"/>
-      <c r="Y45" s="23"/>
+      <c r="U45" s="16"/>
+      <c r="V45" s="19"/>
+      <c r="W45" s="19"/>
+      <c r="X45" s="19"/>
+      <c r="Y45" s="19"/>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
@@ -3588,16 +3636,17 @@
       <c r="C46" t="s">
         <v>13</v>
       </c>
-      <c r="D46" s="12"/>
-      <c r="F46" s="38" t="s">
+      <c r="F46" s="34" t="s">
         <v>258</v>
       </c>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
       <c r="I46" s="2">
         <v>3006</v>
       </c>
-      <c r="J46" s="2"/>
+      <c r="J46" s="2">
+        <v>3006</v>
+      </c>
       <c r="K46" s="2" t="s">
         <v>12</v>
       </c>
@@ -3612,13 +3661,13 @@
       <c r="R46" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S46" s="35"/>
+      <c r="S46" s="31"/>
       <c r="T46" s="10"/>
-      <c r="U46" s="19"/>
-      <c r="V46" s="23"/>
-      <c r="W46" s="23"/>
-      <c r="X46" s="23"/>
-      <c r="Y46" s="23"/>
+      <c r="U46" s="15"/>
+      <c r="V46" s="19"/>
+      <c r="W46" s="19"/>
+      <c r="X46" s="19"/>
+      <c r="Y46" s="19"/>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
@@ -3630,16 +3679,17 @@
       <c r="C47" t="s">
         <v>13</v>
       </c>
-      <c r="D47" s="12"/>
-      <c r="F47" s="38" t="s">
+      <c r="F47" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
       <c r="I47" s="2">
         <v>3006</v>
       </c>
-      <c r="J47" s="2"/>
+      <c r="J47" s="2">
+        <v>3006</v>
+      </c>
       <c r="K47" s="2" t="s">
         <v>12</v>
       </c>
@@ -3654,13 +3704,13 @@
       <c r="R47" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S47" s="35"/>
+      <c r="S47" s="31"/>
       <c r="T47" s="10"/>
-      <c r="U47" s="19"/>
-      <c r="V47" s="23"/>
-      <c r="W47" s="23"/>
-      <c r="X47" s="23"/>
-      <c r="Y47" s="23"/>
+      <c r="U47" s="15"/>
+      <c r="V47" s="19"/>
+      <c r="W47" s="19"/>
+      <c r="X47" s="19"/>
+      <c r="Y47" s="19"/>
     </row>
     <row r="48" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -3672,17 +3722,19 @@
       <c r="C48" t="s">
         <v>13</v>
       </c>
-      <c r="D48" s="12"/>
+      <c r="D48"/>
       <c r="E48"/>
-      <c r="F48" s="39" t="s">
+      <c r="F48" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
       <c r="I48" s="7">
         <v>3006</v>
       </c>
-      <c r="J48"/>
+      <c r="J48" s="2">
+        <v>3006</v>
+      </c>
       <c r="K48" s="2" t="s">
         <v>12</v>
       </c>
@@ -3697,9 +3749,9 @@
       <c r="R48" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S48" s="36"/>
+      <c r="S48" s="32"/>
       <c r="T48"/>
-      <c r="U48" s="21"/>
+      <c r="U48" s="17"/>
       <c r="V48"/>
       <c r="W48"/>
       <c r="X48"/>
@@ -3715,17 +3767,19 @@
       <c r="C49" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="12"/>
+      <c r="D49"/>
       <c r="E49"/>
-      <c r="F49" s="39" t="s">
+      <c r="F49" s="35" t="s">
         <v>260</v>
       </c>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
       <c r="I49" s="7">
         <v>3006</v>
       </c>
-      <c r="J49"/>
+      <c r="J49" s="2">
+        <v>3006</v>
+      </c>
       <c r="K49" s="2" t="s">
         <v>12</v>
       </c>
@@ -3740,9 +3794,9 @@
       <c r="R49" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S49" s="36"/>
+      <c r="S49" s="32"/>
       <c r="T49"/>
-      <c r="U49" s="21"/>
+      <c r="U49" s="17"/>
       <c r="V49"/>
       <c r="W49"/>
       <c r="X49"/>
@@ -3758,17 +3812,19 @@
       <c r="C50" t="s">
         <v>13</v>
       </c>
-      <c r="D50" s="12"/>
+      <c r="D50"/>
       <c r="E50"/>
-      <c r="F50" s="39" t="s">
+      <c r="F50" s="35" t="s">
         <v>261</v>
       </c>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
       <c r="I50" s="7">
         <v>3006</v>
       </c>
-      <c r="J50"/>
+      <c r="J50" s="2">
+        <v>3006</v>
+      </c>
       <c r="K50" s="2" t="s">
         <v>12</v>
       </c>
@@ -3783,9 +3839,9 @@
       <c r="R50" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S50" s="36"/>
+      <c r="S50" s="32"/>
       <c r="T50"/>
-      <c r="U50" s="21"/>
+      <c r="U50" s="17"/>
       <c r="V50"/>
       <c r="W50"/>
       <c r="X50"/>
@@ -3801,17 +3857,19 @@
       <c r="C51" t="s">
         <v>13</v>
       </c>
-      <c r="D51" s="12"/>
+      <c r="D51"/>
       <c r="E51"/>
-      <c r="F51" s="39" t="s">
+      <c r="F51" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
       <c r="I51" s="7">
         <v>3006</v>
       </c>
-      <c r="J51"/>
+      <c r="J51" s="2">
+        <v>3006</v>
+      </c>
       <c r="K51" s="2" t="s">
         <v>12</v>
       </c>
@@ -3826,9 +3884,9 @@
       <c r="R51" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S51" s="36"/>
+      <c r="S51" s="32"/>
       <c r="T51"/>
-      <c r="U51" s="21"/>
+      <c r="U51" s="17"/>
       <c r="V51"/>
       <c r="W51"/>
       <c r="X51"/>
@@ -3844,17 +3902,19 @@
       <c r="C52" t="s">
         <v>13</v>
       </c>
-      <c r="D52" s="12"/>
+      <c r="D52"/>
       <c r="E52"/>
-      <c r="F52" s="39" t="s">
+      <c r="F52" s="35" t="s">
         <v>264</v>
       </c>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
       <c r="I52" s="7">
         <v>3006</v>
       </c>
-      <c r="J52"/>
+      <c r="J52" s="2">
+        <v>3006</v>
+      </c>
       <c r="K52" s="2" t="s">
         <v>12</v>
       </c>
@@ -3869,15 +3929,15 @@
       <c r="R52" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S52" s="36"/>
+      <c r="S52" s="32"/>
       <c r="T52"/>
-      <c r="U52" s="21"/>
+      <c r="U52" s="17"/>
       <c r="V52"/>
       <c r="W52"/>
       <c r="X52"/>
       <c r="Y52"/>
     </row>
-    <row r="53" spans="1:25" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>140</v>
       </c>
@@ -3887,13 +3947,13 @@
       <c r="C53" t="s">
         <v>13</v>
       </c>
-      <c r="D53" s="12"/>
+      <c r="D53"/>
       <c r="E53"/>
-      <c r="F53" s="39" t="s">
+      <c r="F53" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
       <c r="I53" s="7">
         <v>3006</v>
       </c>
@@ -3912,11 +3972,11 @@
       <c r="R53" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="S53" s="35" t="s">
+      <c r="S53" s="31" t="s">
         <v>83</v>
       </c>
       <c r="T53"/>
-      <c r="U53" s="21"/>
+      <c r="U53" s="17"/>
       <c r="V53"/>
       <c r="W53"/>
       <c r="X53"/>
@@ -3932,17 +3992,19 @@
       <c r="C54" t="s">
         <v>13</v>
       </c>
-      <c r="D54" s="12"/>
+      <c r="D54"/>
       <c r="E54"/>
-      <c r="F54" s="39" t="s">
+      <c r="F54" s="35" t="s">
         <v>266</v>
       </c>
-      <c r="G54" s="15"/>
-      <c r="H54" s="15"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
       <c r="I54" s="7">
         <v>3006</v>
       </c>
-      <c r="J54"/>
+      <c r="J54" s="2">
+        <v>3006</v>
+      </c>
       <c r="K54" s="2" t="s">
         <v>12</v>
       </c>
@@ -3957,9 +4019,9 @@
       <c r="R54" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S54" s="36"/>
+      <c r="S54" s="32"/>
       <c r="T54"/>
-      <c r="U54" s="21"/>
+      <c r="U54" s="17"/>
       <c r="V54"/>
       <c r="W54"/>
       <c r="X54"/>
@@ -3975,17 +4037,19 @@
       <c r="C55" t="s">
         <v>13</v>
       </c>
-      <c r="D55" s="12"/>
+      <c r="D55"/>
       <c r="E55"/>
-      <c r="F55" s="39" t="s">
+      <c r="F55" s="35" t="s">
         <v>267</v>
       </c>
-      <c r="G55" s="15"/>
-      <c r="H55" s="15"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
       <c r="I55" s="7">
         <v>3006</v>
       </c>
-      <c r="J55"/>
+      <c r="J55" s="2">
+        <v>3006</v>
+      </c>
       <c r="K55" s="2" t="s">
         <v>12</v>
       </c>
@@ -4000,9 +4064,9 @@
       <c r="R55" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S55" s="36"/>
+      <c r="S55" s="32"/>
       <c r="T55"/>
-      <c r="U55" s="21"/>
+      <c r="U55" s="17"/>
       <c r="V55"/>
       <c r="W55"/>
       <c r="X55"/>
@@ -4018,17 +4082,19 @@
       <c r="C56" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="12"/>
+      <c r="D56"/>
       <c r="E56"/>
-      <c r="F56" s="39" t="s">
+      <c r="F56" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
       <c r="I56" s="7">
         <v>3006</v>
       </c>
-      <c r="J56"/>
+      <c r="J56" s="2">
+        <v>3006</v>
+      </c>
       <c r="K56" s="2" t="s">
         <v>12</v>
       </c>
@@ -4043,9 +4109,9 @@
       <c r="R56" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S56" s="36"/>
+      <c r="S56" s="32"/>
       <c r="T56"/>
-      <c r="U56" s="21"/>
+      <c r="U56" s="17"/>
       <c r="V56"/>
       <c r="W56"/>
       <c r="X56"/>
@@ -4061,17 +4127,19 @@
       <c r="C57" t="s">
         <v>13</v>
       </c>
-      <c r="D57" s="12"/>
+      <c r="D57"/>
       <c r="E57"/>
-      <c r="F57" s="39" t="s">
+      <c r="F57" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
       <c r="I57" s="7">
         <v>3006</v>
       </c>
-      <c r="J57"/>
+      <c r="J57" s="2">
+        <v>3006</v>
+      </c>
       <c r="K57" s="2" t="s">
         <v>12</v>
       </c>
@@ -4086,9 +4154,9 @@
       <c r="R57" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S57" s="36"/>
+      <c r="S57" s="32"/>
       <c r="T57"/>
-      <c r="U57" s="21"/>
+      <c r="U57" s="17"/>
       <c r="V57"/>
       <c r="W57"/>
       <c r="X57"/>
@@ -4104,17 +4172,19 @@
       <c r="C58" t="s">
         <v>13</v>
       </c>
-      <c r="D58" s="12"/>
+      <c r="D58"/>
       <c r="E58"/>
-      <c r="F58" s="39" t="s">
+      <c r="F58" s="35" t="s">
         <v>270</v>
       </c>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
       <c r="I58" s="7">
         <v>3006</v>
       </c>
-      <c r="J58"/>
+      <c r="J58" s="2">
+        <v>3006</v>
+      </c>
       <c r="K58" s="2" t="s">
         <v>12</v>
       </c>
@@ -4129,9 +4199,9 @@
       <c r="R58" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S58" s="36"/>
+      <c r="S58" s="32"/>
       <c r="T58"/>
-      <c r="U58" s="21"/>
+      <c r="U58" s="17"/>
       <c r="V58"/>
       <c r="W58"/>
       <c r="X58"/>
@@ -4147,17 +4217,19 @@
       <c r="C59" t="s">
         <v>13</v>
       </c>
-      <c r="D59" s="12"/>
+      <c r="D59"/>
       <c r="E59"/>
-      <c r="F59" s="39" t="s">
+      <c r="F59" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
       <c r="I59" s="7">
         <v>3006</v>
       </c>
-      <c r="J59"/>
+      <c r="J59" s="2">
+        <v>3006</v>
+      </c>
       <c r="K59" s="2" t="s">
         <v>12</v>
       </c>
@@ -4172,9 +4244,9 @@
       <c r="R59" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S59" s="36"/>
+      <c r="S59" s="32"/>
       <c r="T59"/>
-      <c r="U59" s="21"/>
+      <c r="U59" s="17"/>
       <c r="V59"/>
       <c r="W59"/>
       <c r="X59"/>
@@ -4190,17 +4262,19 @@
       <c r="C60" t="s">
         <v>13</v>
       </c>
-      <c r="D60" s="12"/>
+      <c r="D60"/>
       <c r="E60"/>
-      <c r="F60" s="39" t="s">
+      <c r="F60" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="G60" s="15"/>
-      <c r="H60" s="15"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
       <c r="I60" s="7">
         <v>3006</v>
       </c>
-      <c r="J60"/>
+      <c r="J60" s="2">
+        <v>3006</v>
+      </c>
       <c r="K60" s="2" t="s">
         <v>12</v>
       </c>
@@ -4215,9 +4289,9 @@
       <c r="R60" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S60" s="36"/>
+      <c r="S60" s="32"/>
       <c r="T60"/>
-      <c r="U60" s="21"/>
+      <c r="U60" s="17"/>
       <c r="V60"/>
       <c r="W60"/>
       <c r="X60"/>
@@ -4233,17 +4307,19 @@
       <c r="C61" t="s">
         <v>13</v>
       </c>
-      <c r="D61" s="12"/>
+      <c r="D61"/>
       <c r="E61"/>
-      <c r="F61" s="39" t="s">
+      <c r="F61" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="G61" s="15"/>
-      <c r="H61" s="15"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
       <c r="I61" s="7">
         <v>3006</v>
       </c>
-      <c r="J61"/>
+      <c r="J61" s="2">
+        <v>3006</v>
+      </c>
       <c r="K61" s="2" t="s">
         <v>12</v>
       </c>
@@ -4258,9 +4334,9 @@
       <c r="R61" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S61" s="36"/>
+      <c r="S61" s="32"/>
       <c r="T61"/>
-      <c r="U61" s="21"/>
+      <c r="U61" s="17"/>
       <c r="V61"/>
       <c r="W61"/>
       <c r="X61"/>
@@ -4276,17 +4352,19 @@
       <c r="C62" t="s">
         <v>13</v>
       </c>
-      <c r="D62" s="12"/>
+      <c r="D62"/>
       <c r="E62"/>
-      <c r="F62" s="39" t="s">
+      <c r="F62" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="G62" s="15"/>
-      <c r="H62" s="15"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
       <c r="I62" s="7">
         <v>3006</v>
       </c>
-      <c r="J62"/>
+      <c r="J62" s="2">
+        <v>3006</v>
+      </c>
       <c r="K62" s="2" t="s">
         <v>12</v>
       </c>
@@ -4301,9 +4379,9 @@
       <c r="R62" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S62" s="36"/>
+      <c r="S62" s="32"/>
       <c r="T62"/>
-      <c r="U62" s="21"/>
+      <c r="U62" s="17"/>
       <c r="V62"/>
       <c r="W62"/>
       <c r="X62"/>
@@ -4319,17 +4397,19 @@
       <c r="C63" t="s">
         <v>13</v>
       </c>
-      <c r="D63" s="12"/>
+      <c r="D63"/>
       <c r="E63"/>
-      <c r="F63" s="39" t="s">
+      <c r="F63" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="G63" s="15"/>
-      <c r="H63" s="15"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
       <c r="I63" s="7">
         <v>3006</v>
       </c>
-      <c r="J63"/>
+      <c r="J63" s="2">
+        <v>3006</v>
+      </c>
       <c r="K63" s="2" t="s">
         <v>12</v>
       </c>
@@ -4344,9 +4424,9 @@
       <c r="R63" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S63" s="36"/>
+      <c r="S63" s="32"/>
       <c r="T63"/>
-      <c r="U63" s="21"/>
+      <c r="U63" s="17"/>
       <c r="V63"/>
       <c r="W63"/>
       <c r="X63"/>
@@ -4362,17 +4442,19 @@
       <c r="C64" t="s">
         <v>13</v>
       </c>
-      <c r="D64" s="12"/>
+      <c r="D64"/>
       <c r="E64"/>
-      <c r="F64" s="39" t="s">
+      <c r="F64" s="35" t="s">
         <v>276</v>
       </c>
-      <c r="G64" s="15"/>
-      <c r="H64" s="15"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
       <c r="I64" s="7">
         <v>3006</v>
       </c>
-      <c r="J64"/>
+      <c r="J64" s="2">
+        <v>3006</v>
+      </c>
       <c r="K64" s="2" t="s">
         <v>12</v>
       </c>
@@ -4387,9 +4469,9 @@
       <c r="R64" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S64" s="36"/>
+      <c r="S64" s="32"/>
       <c r="T64"/>
-      <c r="U64" s="21"/>
+      <c r="U64" s="17"/>
       <c r="V64"/>
       <c r="W64"/>
       <c r="X64"/>
@@ -4405,17 +4487,19 @@
       <c r="C65" t="s">
         <v>13</v>
       </c>
-      <c r="D65" s="12"/>
+      <c r="D65"/>
       <c r="E65"/>
-      <c r="F65" s="39" t="s">
+      <c r="F65" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="G65" s="15"/>
-      <c r="H65" s="15"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
       <c r="I65" s="7">
         <v>3006</v>
       </c>
-      <c r="J65"/>
+      <c r="J65" s="2">
+        <v>3006</v>
+      </c>
       <c r="K65" s="2" t="s">
         <v>12</v>
       </c>
@@ -4430,9 +4514,9 @@
       <c r="R65" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S65" s="36"/>
+      <c r="S65" s="32"/>
       <c r="T65"/>
-      <c r="U65" s="21"/>
+      <c r="U65" s="17"/>
       <c r="V65"/>
       <c r="W65"/>
       <c r="X65"/>
@@ -4448,17 +4532,19 @@
       <c r="C66" t="s">
         <v>13</v>
       </c>
-      <c r="D66" s="12"/>
+      <c r="D66"/>
       <c r="E66"/>
-      <c r="F66" s="39" t="s">
+      <c r="F66" s="35" t="s">
         <v>278</v>
       </c>
-      <c r="G66" s="15"/>
-      <c r="H66" s="15"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
       <c r="I66" s="7">
         <v>3006</v>
       </c>
-      <c r="J66"/>
+      <c r="J66" s="2">
+        <v>3006</v>
+      </c>
       <c r="K66" s="2" t="s">
         <v>12</v>
       </c>
@@ -4473,9 +4559,9 @@
       <c r="R66" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S66" s="36"/>
+      <c r="S66" s="32"/>
       <c r="T66"/>
-      <c r="U66" s="21"/>
+      <c r="U66" s="17"/>
       <c r="V66"/>
       <c r="W66"/>
       <c r="X66"/>
@@ -4491,17 +4577,19 @@
       <c r="C67" t="s">
         <v>13</v>
       </c>
-      <c r="D67" s="12"/>
+      <c r="D67"/>
       <c r="E67"/>
-      <c r="F67" s="39" t="s">
+      <c r="F67" s="35" t="s">
         <v>279</v>
       </c>
-      <c r="G67" s="15"/>
-      <c r="H67" s="15"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
       <c r="I67" s="7">
         <v>3006</v>
       </c>
-      <c r="J67"/>
+      <c r="J67" s="2">
+        <v>3006</v>
+      </c>
       <c r="K67" s="2" t="s">
         <v>12</v>
       </c>
@@ -4516,9 +4604,9 @@
       <c r="R67" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S67" s="36"/>
+      <c r="S67" s="32"/>
       <c r="T67"/>
-      <c r="U67" s="21"/>
+      <c r="U67" s="17"/>
       <c r="V67"/>
       <c r="W67"/>
       <c r="X67"/>
@@ -4534,17 +4622,19 @@
       <c r="C68" t="s">
         <v>13</v>
       </c>
-      <c r="D68" s="12"/>
+      <c r="D68"/>
       <c r="E68"/>
-      <c r="F68" s="39" t="s">
+      <c r="F68" s="35" t="s">
         <v>280</v>
       </c>
-      <c r="G68" s="15"/>
-      <c r="H68" s="15"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
       <c r="I68" s="7">
         <v>3006</v>
       </c>
-      <c r="J68"/>
+      <c r="J68" s="2">
+        <v>3006</v>
+      </c>
       <c r="K68" s="2" t="s">
         <v>12</v>
       </c>
@@ -4559,9 +4649,9 @@
       <c r="R68" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S68" s="36"/>
+      <c r="S68" s="32"/>
       <c r="T68"/>
-      <c r="U68" s="21"/>
+      <c r="U68" s="17"/>
       <c r="V68"/>
       <c r="W68"/>
       <c r="X68"/>
@@ -4577,17 +4667,19 @@
       <c r="C69" t="s">
         <v>13</v>
       </c>
-      <c r="D69" s="12"/>
+      <c r="D69"/>
       <c r="E69"/>
-      <c r="F69" s="39" t="s">
+      <c r="F69" s="35" t="s">
         <v>281</v>
       </c>
-      <c r="G69" s="15"/>
-      <c r="H69" s="15"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
       <c r="I69" s="7">
         <v>3006</v>
       </c>
-      <c r="J69"/>
+      <c r="J69" s="2">
+        <v>3006</v>
+      </c>
       <c r="K69" s="2" t="s">
         <v>12</v>
       </c>
@@ -4602,9 +4694,9 @@
       <c r="R69" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S69" s="36"/>
+      <c r="S69" s="32"/>
       <c r="T69"/>
-      <c r="U69" s="21"/>
+      <c r="U69" s="17"/>
       <c r="V69"/>
       <c r="W69"/>
       <c r="X69"/>
@@ -4620,17 +4712,19 @@
       <c r="C70" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="12"/>
+      <c r="D70"/>
       <c r="E70"/>
-      <c r="F70" s="39" t="s">
+      <c r="F70" s="35" t="s">
         <v>282</v>
       </c>
-      <c r="G70" s="15"/>
-      <c r="H70" s="15"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
       <c r="I70" s="7">
         <v>3006</v>
       </c>
-      <c r="J70"/>
+      <c r="J70" s="2">
+        <v>3006</v>
+      </c>
       <c r="K70" s="2" t="s">
         <v>12</v>
       </c>
@@ -4645,9 +4739,9 @@
       <c r="R70" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S70" s="36"/>
+      <c r="S70" s="32"/>
       <c r="T70"/>
-      <c r="U70" s="21"/>
+      <c r="U70" s="17"/>
       <c r="V70"/>
       <c r="W70"/>
       <c r="X70"/>
@@ -4663,17 +4757,19 @@
       <c r="C71" t="s">
         <v>13</v>
       </c>
-      <c r="D71" s="12"/>
+      <c r="D71"/>
       <c r="E71"/>
-      <c r="F71" s="39" t="s">
+      <c r="F71" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="G71" s="15"/>
-      <c r="H71" s="15"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
       <c r="I71" s="7">
         <v>3006</v>
       </c>
-      <c r="J71"/>
+      <c r="J71" s="2">
+        <v>3006</v>
+      </c>
       <c r="K71" s="2" t="s">
         <v>12</v>
       </c>
@@ -4688,9 +4784,9 @@
       <c r="R71" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S71" s="36"/>
+      <c r="S71" s="32"/>
       <c r="T71"/>
-      <c r="U71" s="21"/>
+      <c r="U71" s="17"/>
       <c r="V71"/>
       <c r="W71"/>
       <c r="X71"/>
@@ -4706,17 +4802,19 @@
       <c r="C72" t="s">
         <v>13</v>
       </c>
-      <c r="D72" s="12"/>
+      <c r="D72"/>
       <c r="E72"/>
-      <c r="F72" s="39" t="s">
+      <c r="F72" s="35" t="s">
         <v>284</v>
       </c>
-      <c r="G72" s="15"/>
-      <c r="H72" s="15"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
       <c r="I72" s="7">
         <v>3006</v>
       </c>
-      <c r="J72"/>
+      <c r="J72" s="2">
+        <v>3006</v>
+      </c>
       <c r="K72" s="2" t="s">
         <v>12</v>
       </c>
@@ -4731,9 +4829,9 @@
       <c r="R72" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S72" s="36"/>
+      <c r="S72" s="32"/>
       <c r="T72"/>
-      <c r="U72" s="21"/>
+      <c r="U72" s="17"/>
       <c r="V72"/>
       <c r="W72"/>
       <c r="X72"/>
@@ -4749,17 +4847,19 @@
       <c r="C73" t="s">
         <v>13</v>
       </c>
-      <c r="D73" s="12"/>
+      <c r="D73"/>
       <c r="E73"/>
-      <c r="F73" s="39" t="s">
+      <c r="F73" s="35" t="s">
         <v>285</v>
       </c>
-      <c r="G73" s="15"/>
-      <c r="H73" s="15"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
       <c r="I73" s="7">
         <v>3006</v>
       </c>
-      <c r="J73"/>
+      <c r="J73" s="2">
+        <v>3006</v>
+      </c>
       <c r="K73" s="2" t="s">
         <v>12</v>
       </c>
@@ -4774,9 +4874,9 @@
       <c r="R73" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S73" s="36"/>
+      <c r="S73" s="32"/>
       <c r="T73"/>
-      <c r="U73" s="21"/>
+      <c r="U73" s="17"/>
       <c r="V73"/>
       <c r="W73"/>
       <c r="X73"/>
@@ -4792,17 +4892,19 @@
       <c r="C74" t="s">
         <v>13</v>
       </c>
-      <c r="D74" s="12"/>
+      <c r="D74"/>
       <c r="E74"/>
-      <c r="F74" s="39" t="s">
+      <c r="F74" s="35" t="s">
         <v>232</v>
       </c>
-      <c r="G74" s="15"/>
-      <c r="H74" s="15"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
       <c r="I74" s="7">
         <v>3006</v>
       </c>
-      <c r="J74"/>
+      <c r="J74" s="2">
+        <v>3006</v>
+      </c>
       <c r="K74" s="2" t="s">
         <v>12</v>
       </c>
@@ -4817,9 +4919,9 @@
       <c r="R74" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S74" s="36"/>
+      <c r="S74" s="32"/>
       <c r="T74"/>
-      <c r="U74" s="21"/>
+      <c r="U74" s="17"/>
       <c r="V74"/>
       <c r="W74"/>
       <c r="X74"/>
@@ -4835,17 +4937,19 @@
       <c r="C75" t="s">
         <v>13</v>
       </c>
-      <c r="D75" s="12"/>
+      <c r="D75"/>
       <c r="E75"/>
-      <c r="F75" s="39" t="s">
+      <c r="F75" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="G75" s="15"/>
-      <c r="H75" s="15"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
       <c r="I75" s="7">
         <v>3006</v>
       </c>
-      <c r="J75"/>
+      <c r="J75" s="2">
+        <v>3006</v>
+      </c>
       <c r="K75" s="2" t="s">
         <v>12</v>
       </c>
@@ -4860,9 +4964,9 @@
       <c r="R75" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S75" s="36"/>
+      <c r="S75" s="32"/>
       <c r="T75"/>
-      <c r="U75" s="21"/>
+      <c r="U75" s="17"/>
       <c r="V75"/>
       <c r="W75"/>
       <c r="X75"/>
@@ -4878,17 +4982,19 @@
       <c r="C76" t="s">
         <v>13</v>
       </c>
-      <c r="D76" s="12"/>
+      <c r="D76"/>
       <c r="E76"/>
-      <c r="F76" s="39" t="s">
+      <c r="F76" s="35" t="s">
         <v>287</v>
       </c>
-      <c r="G76" s="15"/>
-      <c r="H76" s="15"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
       <c r="I76" s="7">
         <v>3006</v>
       </c>
-      <c r="J76"/>
+      <c r="J76" s="2">
+        <v>3006</v>
+      </c>
       <c r="K76" s="2" t="s">
         <v>12</v>
       </c>
@@ -4903,9 +5009,9 @@
       <c r="R76" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S76" s="36"/>
+      <c r="S76" s="32"/>
       <c r="T76"/>
-      <c r="U76" s="21"/>
+      <c r="U76" s="17"/>
       <c r="V76"/>
       <c r="W76"/>
       <c r="X76"/>
@@ -4921,17 +5027,19 @@
       <c r="C77" t="s">
         <v>13</v>
       </c>
-      <c r="D77" s="12"/>
+      <c r="D77"/>
       <c r="E77"/>
-      <c r="F77" s="39" t="s">
+      <c r="F77" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="G77" s="15"/>
-      <c r="H77" s="15"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
       <c r="I77" s="7">
         <v>3006</v>
       </c>
-      <c r="J77"/>
+      <c r="J77" s="2">
+        <v>3006</v>
+      </c>
       <c r="K77" s="2" t="s">
         <v>12</v>
       </c>
@@ -4948,9 +5056,9 @@
       <c r="R77" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S77" s="36"/>
+      <c r="S77" s="32"/>
       <c r="T77"/>
-      <c r="U77" s="21"/>
+      <c r="U77" s="17"/>
       <c r="V77"/>
       <c r="W77"/>
       <c r="X77"/>
@@ -4966,17 +5074,19 @@
       <c r="C78" t="s">
         <v>13</v>
       </c>
-      <c r="D78" s="12"/>
+      <c r="D78"/>
       <c r="E78"/>
-      <c r="F78" s="39" t="s">
+      <c r="F78" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="G78" s="15"/>
-      <c r="H78" s="15"/>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
       <c r="I78" s="7">
         <v>3006</v>
       </c>
-      <c r="J78"/>
+      <c r="J78" s="2">
+        <v>3006</v>
+      </c>
       <c r="K78" s="2" t="s">
         <v>12</v>
       </c>
@@ -4993,9 +5103,9 @@
       <c r="R78" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S78" s="36"/>
+      <c r="S78" s="32"/>
       <c r="T78"/>
-      <c r="U78" s="21"/>
+      <c r="U78" s="17"/>
       <c r="V78"/>
       <c r="W78"/>
       <c r="X78"/>
@@ -5011,17 +5121,19 @@
       <c r="C79" t="s">
         <v>13</v>
       </c>
-      <c r="D79" s="12"/>
+      <c r="D79"/>
       <c r="E79"/>
-      <c r="F79" s="39" t="s">
+      <c r="F79" s="35" t="s">
         <v>290</v>
       </c>
-      <c r="G79" s="15"/>
-      <c r="H79" s="15"/>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
       <c r="I79" s="7">
         <v>3006</v>
       </c>
-      <c r="J79"/>
+      <c r="J79" s="2">
+        <v>3006</v>
+      </c>
       <c r="K79" s="2" t="s">
         <v>12</v>
       </c>
@@ -5038,9 +5150,9 @@
       <c r="R79" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S79" s="36"/>
+      <c r="S79" s="32"/>
       <c r="T79"/>
-      <c r="U79" s="21"/>
+      <c r="U79" s="17"/>
       <c r="V79"/>
       <c r="W79"/>
       <c r="X79"/>
@@ -5056,17 +5168,19 @@
       <c r="C80" t="s">
         <v>13</v>
       </c>
-      <c r="D80" s="12"/>
+      <c r="D80"/>
       <c r="E80"/>
-      <c r="F80" s="39" t="s">
+      <c r="F80" s="35" t="s">
         <v>291</v>
       </c>
-      <c r="G80" s="15"/>
-      <c r="H80" s="15"/>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
       <c r="I80" s="7">
         <v>3006</v>
       </c>
-      <c r="J80"/>
+      <c r="J80" s="2">
+        <v>3006</v>
+      </c>
       <c r="K80" s="2" t="s">
         <v>12</v>
       </c>
@@ -5083,9 +5197,9 @@
       <c r="R80" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S80" s="36"/>
+      <c r="S80" s="32"/>
       <c r="T80"/>
-      <c r="U80" s="21"/>
+      <c r="U80" s="17"/>
       <c r="V80"/>
       <c r="W80"/>
       <c r="X80"/>
@@ -5101,17 +5215,19 @@
       <c r="C81" t="s">
         <v>13</v>
       </c>
-      <c r="D81" s="12"/>
+      <c r="D81"/>
       <c r="E81"/>
-      <c r="F81" s="39" t="s">
+      <c r="F81" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="G81" s="15"/>
-      <c r="H81" s="15"/>
+      <c r="G81" s="13"/>
+      <c r="H81" s="13"/>
       <c r="I81" s="7">
         <v>3006</v>
       </c>
-      <c r="J81"/>
+      <c r="J81" s="2">
+        <v>3006</v>
+      </c>
       <c r="K81" s="2" t="s">
         <v>12</v>
       </c>
@@ -5128,15 +5244,15 @@
       <c r="R81" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S81" s="36"/>
+      <c r="S81" s="32"/>
       <c r="T81"/>
-      <c r="U81" s="21"/>
+      <c r="U81" s="17"/>
       <c r="V81"/>
       <c r="W81"/>
       <c r="X81"/>
       <c r="Y81"/>
     </row>
-    <row r="82" spans="1:25" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>169</v>
       </c>
@@ -5146,13 +5262,13 @@
       <c r="C82" t="s">
         <v>13</v>
       </c>
-      <c r="D82" s="12"/>
+      <c r="D82"/>
       <c r="E82"/>
-      <c r="F82" s="39" t="s">
+      <c r="F82" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="G82" s="15"/>
-      <c r="H82" s="15"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="13"/>
       <c r="I82" s="7">
         <v>3006</v>
       </c>
@@ -5173,11 +5289,11 @@
       <c r="R82" t="s">
         <v>13</v>
       </c>
-      <c r="S82" s="35" t="s">
+      <c r="S82" s="31" t="s">
         <v>83</v>
       </c>
       <c r="T82"/>
-      <c r="U82" s="21"/>
+      <c r="U82" s="17"/>
       <c r="V82"/>
       <c r="W82"/>
       <c r="X82"/>
@@ -5193,17 +5309,19 @@
       <c r="C83" t="s">
         <v>13</v>
       </c>
-      <c r="D83" s="12"/>
+      <c r="D83"/>
       <c r="E83"/>
-      <c r="F83" s="39" t="s">
+      <c r="F83" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="G83" s="15"/>
-      <c r="H83" s="15"/>
+      <c r="G83" s="13"/>
+      <c r="H83" s="13"/>
       <c r="I83" s="7">
         <v>3006</v>
       </c>
-      <c r="J83"/>
+      <c r="J83" s="2">
+        <v>3006</v>
+      </c>
       <c r="K83" s="2" t="s">
         <v>12</v>
       </c>
@@ -5220,9 +5338,9 @@
       <c r="R83" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S83" s="36"/>
+      <c r="S83" s="32"/>
       <c r="T83"/>
-      <c r="U83" s="21"/>
+      <c r="U83" s="17"/>
       <c r="V83"/>
       <c r="W83"/>
       <c r="X83"/>
@@ -5238,17 +5356,19 @@
       <c r="C84" t="s">
         <v>13</v>
       </c>
-      <c r="D84" s="12"/>
+      <c r="D84"/>
       <c r="E84"/>
-      <c r="F84" s="39" t="s">
+      <c r="F84" s="35" t="s">
         <v>294</v>
       </c>
-      <c r="G84" s="15"/>
-      <c r="H84" s="15"/>
+      <c r="G84" s="13"/>
+      <c r="H84" s="13"/>
       <c r="I84" s="7">
         <v>3006</v>
       </c>
-      <c r="J84"/>
+      <c r="J84" s="2">
+        <v>3006</v>
+      </c>
       <c r="K84" s="2" t="s">
         <v>12</v>
       </c>
@@ -5265,9 +5385,9 @@
       <c r="R84" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S84" s="36"/>
+      <c r="S84" s="32"/>
       <c r="T84"/>
-      <c r="U84" s="21"/>
+      <c r="U84" s="17"/>
       <c r="V84"/>
       <c r="W84"/>
       <c r="X84"/>
@@ -5283,17 +5403,19 @@
       <c r="C85" t="s">
         <v>13</v>
       </c>
-      <c r="D85" s="12"/>
+      <c r="D85"/>
       <c r="E85"/>
-      <c r="F85" s="39" t="s">
+      <c r="F85" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="G85" s="15"/>
-      <c r="H85" s="15"/>
+      <c r="G85" s="13"/>
+      <c r="H85" s="13"/>
       <c r="I85" s="7">
         <v>3006</v>
       </c>
-      <c r="J85"/>
+      <c r="J85" s="2">
+        <v>3006</v>
+      </c>
       <c r="K85" s="2" t="s">
         <v>12</v>
       </c>
@@ -5310,9 +5432,9 @@
       <c r="R85" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S85" s="36"/>
+      <c r="S85" s="32"/>
       <c r="T85"/>
-      <c r="U85" s="21"/>
+      <c r="U85" s="17"/>
       <c r="V85"/>
       <c r="W85"/>
       <c r="X85"/>
@@ -5328,17 +5450,19 @@
       <c r="C86" t="s">
         <v>13</v>
       </c>
-      <c r="D86" s="12"/>
+      <c r="D86"/>
       <c r="E86"/>
-      <c r="F86" s="39" t="s">
+      <c r="F86" s="35" t="s">
         <v>296</v>
       </c>
-      <c r="G86" s="15"/>
-      <c r="H86" s="15"/>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
       <c r="I86" s="7">
         <v>3006</v>
       </c>
-      <c r="J86"/>
+      <c r="J86" s="2">
+        <v>3006</v>
+      </c>
       <c r="K86" s="2" t="s">
         <v>12</v>
       </c>
@@ -5355,9 +5479,9 @@
       <c r="R86" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S86" s="36"/>
+      <c r="S86" s="32"/>
       <c r="T86"/>
-      <c r="U86" s="21"/>
+      <c r="U86" s="17"/>
       <c r="V86"/>
       <c r="W86"/>
       <c r="X86"/>
@@ -5373,17 +5497,19 @@
       <c r="C87" t="s">
         <v>13</v>
       </c>
-      <c r="D87" s="12"/>
+      <c r="D87"/>
       <c r="E87"/>
-      <c r="F87" s="39" t="s">
+      <c r="F87" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="G87" s="15"/>
-      <c r="H87" s="15"/>
+      <c r="G87" s="13"/>
+      <c r="H87" s="13"/>
       <c r="I87" s="7">
         <v>3006</v>
       </c>
-      <c r="J87"/>
+      <c r="J87" s="2">
+        <v>3006</v>
+      </c>
       <c r="K87" s="2" t="s">
         <v>12</v>
       </c>
@@ -5400,9 +5526,9 @@
       <c r="R87" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S87" s="36"/>
+      <c r="S87" s="32"/>
       <c r="T87"/>
-      <c r="U87" s="21"/>
+      <c r="U87" s="17"/>
       <c r="V87"/>
       <c r="W87"/>
       <c r="X87"/>
@@ -5418,17 +5544,19 @@
       <c r="C88" t="s">
         <v>13</v>
       </c>
-      <c r="D88" s="12"/>
+      <c r="D88"/>
       <c r="E88"/>
-      <c r="F88" s="39" t="s">
+      <c r="F88" s="35" t="s">
         <v>297</v>
       </c>
-      <c r="G88" s="15"/>
-      <c r="H88" s="15"/>
+      <c r="G88" s="13"/>
+      <c r="H88" s="13"/>
       <c r="I88" s="7">
         <v>3006</v>
       </c>
-      <c r="J88"/>
+      <c r="J88" s="2">
+        <v>3006</v>
+      </c>
       <c r="K88" s="2" t="s">
         <v>12</v>
       </c>
@@ -5445,9 +5573,9 @@
       <c r="R88" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S88" s="36"/>
+      <c r="S88" s="32"/>
       <c r="T88"/>
-      <c r="U88" s="21"/>
+      <c r="U88" s="17"/>
       <c r="V88"/>
       <c r="W88"/>
       <c r="X88"/>
@@ -5463,17 +5591,19 @@
       <c r="C89" t="s">
         <v>13</v>
       </c>
-      <c r="D89" s="12"/>
+      <c r="D89"/>
       <c r="E89"/>
-      <c r="F89" s="39" t="s">
+      <c r="F89" s="35" t="s">
         <v>298</v>
       </c>
-      <c r="G89" s="15"/>
-      <c r="H89" s="15"/>
+      <c r="G89" s="13"/>
+      <c r="H89" s="13"/>
       <c r="I89" s="7">
         <v>3006</v>
       </c>
-      <c r="J89"/>
+      <c r="J89" s="2">
+        <v>3006</v>
+      </c>
       <c r="K89" s="2" t="s">
         <v>12</v>
       </c>
@@ -5490,9 +5620,9 @@
       <c r="R89" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S89" s="36"/>
+      <c r="S89" s="32"/>
       <c r="T89"/>
-      <c r="U89" s="21"/>
+      <c r="U89" s="17"/>
       <c r="V89"/>
       <c r="W89"/>
       <c r="X89"/>
@@ -5508,17 +5638,19 @@
       <c r="C90" t="s">
         <v>13</v>
       </c>
-      <c r="D90" s="12"/>
+      <c r="D90"/>
       <c r="E90"/>
-      <c r="F90" s="39" t="s">
+      <c r="F90" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="G90" s="15"/>
-      <c r="H90" s="15"/>
+      <c r="G90" s="13"/>
+      <c r="H90" s="13"/>
       <c r="I90" s="7">
         <v>3006</v>
       </c>
-      <c r="J90"/>
+      <c r="J90" s="2">
+        <v>3006</v>
+      </c>
       <c r="K90" s="2" t="s">
         <v>12</v>
       </c>
@@ -5535,9 +5667,9 @@
       <c r="R90" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S90" s="36"/>
+      <c r="S90" s="32"/>
       <c r="T90"/>
-      <c r="U90" s="21"/>
+      <c r="U90" s="17"/>
       <c r="V90"/>
       <c r="W90"/>
       <c r="X90"/>
@@ -5553,17 +5685,19 @@
       <c r="C91" t="s">
         <v>13</v>
       </c>
-      <c r="D91" s="12"/>
+      <c r="D91"/>
       <c r="E91"/>
-      <c r="F91" s="39" t="s">
+      <c r="F91" s="35" t="s">
         <v>300</v>
       </c>
-      <c r="G91" s="15"/>
-      <c r="H91" s="15"/>
+      <c r="G91" s="13"/>
+      <c r="H91" s="13"/>
       <c r="I91" s="7">
         <v>3006</v>
       </c>
-      <c r="J91"/>
+      <c r="J91" s="2">
+        <v>3006</v>
+      </c>
       <c r="K91" s="2" t="s">
         <v>12</v>
       </c>
@@ -5580,9 +5714,9 @@
       <c r="R91" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S91" s="36"/>
+      <c r="S91" s="32"/>
       <c r="T91"/>
-      <c r="U91" s="21"/>
+      <c r="U91" s="17"/>
       <c r="V91"/>
       <c r="W91"/>
       <c r="X91"/>
@@ -5598,17 +5732,19 @@
       <c r="C92" t="s">
         <v>13</v>
       </c>
-      <c r="D92" s="12"/>
+      <c r="D92"/>
       <c r="E92"/>
-      <c r="F92" s="39" t="s">
+      <c r="F92" s="35" t="s">
         <v>301</v>
       </c>
-      <c r="G92" s="15"/>
-      <c r="H92" s="15"/>
+      <c r="G92" s="13"/>
+      <c r="H92" s="13"/>
       <c r="I92" s="7">
         <v>3006</v>
       </c>
-      <c r="J92"/>
+      <c r="J92" s="2">
+        <v>3006</v>
+      </c>
       <c r="K92" s="2" t="s">
         <v>12</v>
       </c>
@@ -5625,9 +5761,9 @@
       <c r="R92" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S92" s="36"/>
+      <c r="S92" s="32"/>
       <c r="T92"/>
-      <c r="U92" s="21"/>
+      <c r="U92" s="17"/>
       <c r="V92"/>
       <c r="W92"/>
       <c r="X92"/>
@@ -5643,17 +5779,19 @@
       <c r="C93" t="s">
         <v>13</v>
       </c>
-      <c r="D93" s="12"/>
+      <c r="D93"/>
       <c r="E93"/>
-      <c r="F93" s="39" t="s">
+      <c r="F93" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="G93" s="15"/>
-      <c r="H93" s="15"/>
+      <c r="G93" s="13"/>
+      <c r="H93" s="13"/>
       <c r="I93" s="7">
         <v>3006</v>
       </c>
-      <c r="J93"/>
+      <c r="J93" s="2">
+        <v>3006</v>
+      </c>
       <c r="K93" s="2" t="s">
         <v>12</v>
       </c>
@@ -5670,9 +5808,9 @@
       <c r="R93" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S93" s="36"/>
+      <c r="S93" s="32"/>
       <c r="T93"/>
-      <c r="U93" s="21"/>
+      <c r="U93" s="17"/>
       <c r="V93"/>
       <c r="W93"/>
       <c r="X93"/>
@@ -5688,17 +5826,19 @@
       <c r="C94" t="s">
         <v>13</v>
       </c>
-      <c r="D94" s="12"/>
+      <c r="D94"/>
       <c r="E94"/>
-      <c r="F94" s="39" t="s">
+      <c r="F94" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="G94" s="15"/>
-      <c r="H94" s="15"/>
+      <c r="G94" s="13"/>
+      <c r="H94" s="13"/>
       <c r="I94" s="7">
         <v>3006</v>
       </c>
-      <c r="J94"/>
+      <c r="J94" s="2">
+        <v>3006</v>
+      </c>
       <c r="K94" s="2" t="s">
         <v>12</v>
       </c>
@@ -5715,9 +5855,9 @@
       <c r="R94" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S94" s="36"/>
+      <c r="S94" s="32"/>
       <c r="T94"/>
-      <c r="U94" s="21"/>
+      <c r="U94" s="17"/>
       <c r="V94"/>
       <c r="W94"/>
       <c r="X94"/>
@@ -5733,17 +5873,19 @@
       <c r="C95" t="s">
         <v>13</v>
       </c>
-      <c r="D95" s="12"/>
+      <c r="D95"/>
       <c r="E95"/>
-      <c r="F95" s="39" t="s">
+      <c r="F95" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="G95" s="15"/>
-      <c r="H95" s="15"/>
+      <c r="G95" s="13"/>
+      <c r="H95" s="13"/>
       <c r="I95" s="7">
         <v>3006</v>
       </c>
-      <c r="J95"/>
+      <c r="J95" s="2">
+        <v>3006</v>
+      </c>
       <c r="K95" s="2" t="s">
         <v>12</v>
       </c>
@@ -5760,9 +5902,9 @@
       <c r="R95" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S95" s="36"/>
+      <c r="S95" s="32"/>
       <c r="T95"/>
-      <c r="U95" s="21"/>
+      <c r="U95" s="17"/>
       <c r="V95"/>
       <c r="W95"/>
       <c r="X95"/>
@@ -5778,17 +5920,19 @@
       <c r="C96" t="s">
         <v>13</v>
       </c>
-      <c r="D96" s="12"/>
+      <c r="D96"/>
       <c r="E96"/>
-      <c r="F96" s="39" t="s">
+      <c r="F96" s="35" t="s">
         <v>305</v>
       </c>
-      <c r="G96" s="15"/>
-      <c r="H96" s="15"/>
+      <c r="G96" s="13"/>
+      <c r="H96" s="13"/>
       <c r="I96" s="7">
         <v>3006</v>
       </c>
-      <c r="J96"/>
+      <c r="J96" s="2">
+        <v>3006</v>
+      </c>
       <c r="K96" s="2" t="s">
         <v>12</v>
       </c>
@@ -5805,9 +5949,9 @@
       <c r="R96" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S96" s="36"/>
+      <c r="S96" s="32"/>
       <c r="T96"/>
-      <c r="U96" s="21"/>
+      <c r="U96" s="17"/>
       <c r="V96"/>
       <c r="W96"/>
       <c r="X96"/>
@@ -5823,17 +5967,19 @@
       <c r="C97" t="s">
         <v>13</v>
       </c>
-      <c r="D97" s="12"/>
+      <c r="D97"/>
       <c r="E97"/>
-      <c r="F97" s="39" t="s">
+      <c r="F97" s="35" t="s">
         <v>306</v>
       </c>
-      <c r="G97" s="15"/>
-      <c r="H97" s="15"/>
+      <c r="G97" s="13"/>
+      <c r="H97" s="13"/>
       <c r="I97" s="7">
         <v>3006</v>
       </c>
-      <c r="J97"/>
+      <c r="J97" s="2">
+        <v>3006</v>
+      </c>
       <c r="K97" s="2" t="s">
         <v>12</v>
       </c>
@@ -5850,9 +5996,9 @@
       <c r="R97" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S97" s="36"/>
+      <c r="S97" s="32"/>
       <c r="T97"/>
-      <c r="U97" s="21"/>
+      <c r="U97" s="17"/>
       <c r="V97"/>
       <c r="W97"/>
       <c r="X97"/>
@@ -5868,17 +6014,19 @@
       <c r="C98" t="s">
         <v>13</v>
       </c>
-      <c r="D98" s="12"/>
+      <c r="D98"/>
       <c r="E98"/>
-      <c r="F98" s="39" t="s">
+      <c r="F98" s="35" t="s">
         <v>307</v>
       </c>
-      <c r="G98" s="15"/>
-      <c r="H98" s="15"/>
+      <c r="G98" s="13"/>
+      <c r="H98" s="13"/>
       <c r="I98" s="7">
         <v>3006</v>
       </c>
-      <c r="J98"/>
+      <c r="J98" s="2">
+        <v>3006</v>
+      </c>
       <c r="K98" s="2" t="s">
         <v>12</v>
       </c>
@@ -5895,9 +6043,9 @@
       <c r="R98" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S98" s="36"/>
+      <c r="S98" s="32"/>
       <c r="T98"/>
-      <c r="U98" s="21"/>
+      <c r="U98" s="17"/>
       <c r="V98"/>
       <c r="W98"/>
       <c r="X98"/>
@@ -5913,17 +6061,19 @@
       <c r="C99" t="s">
         <v>13</v>
       </c>
-      <c r="D99" s="12"/>
+      <c r="D99"/>
       <c r="E99"/>
-      <c r="F99" s="39" t="s">
+      <c r="F99" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="G99" s="15"/>
-      <c r="H99" s="15"/>
+      <c r="G99" s="13"/>
+      <c r="H99" s="13"/>
       <c r="I99" s="7">
         <v>3006</v>
       </c>
-      <c r="J99"/>
+      <c r="J99" s="2">
+        <v>3006</v>
+      </c>
       <c r="K99" s="2" t="s">
         <v>12</v>
       </c>
@@ -5940,15 +6090,15 @@
       <c r="R99" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S99" s="36"/>
+      <c r="S99" s="32"/>
       <c r="T99"/>
-      <c r="U99" s="21"/>
+      <c r="U99" s="17"/>
       <c r="V99"/>
       <c r="W99"/>
       <c r="X99"/>
       <c r="Y99"/>
     </row>
-    <row r="100" spans="1:25" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>187</v>
       </c>
@@ -5958,13 +6108,13 @@
       <c r="C100" t="s">
         <v>13</v>
       </c>
-      <c r="D100" s="12"/>
+      <c r="D100"/>
       <c r="E100"/>
-      <c r="F100" s="39" t="s">
+      <c r="F100" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="G100" s="15"/>
-      <c r="H100" s="15"/>
+      <c r="G100" s="13"/>
+      <c r="H100" s="13"/>
       <c r="I100" s="7">
         <v>3011</v>
       </c>
@@ -5985,11 +6135,11 @@
       <c r="R100" t="s">
         <v>13</v>
       </c>
-      <c r="S100" s="35" t="s">
+      <c r="S100" s="31" t="s">
         <v>83</v>
       </c>
       <c r="T100"/>
-      <c r="U100" s="21"/>
+      <c r="U100" s="17"/>
       <c r="V100"/>
       <c r="W100"/>
       <c r="X100"/>
@@ -6005,17 +6155,19 @@
       <c r="C101" t="s">
         <v>13</v>
       </c>
-      <c r="D101" s="12"/>
+      <c r="D101"/>
       <c r="E101"/>
-      <c r="F101" s="39" t="s">
+      <c r="F101" s="35" t="s">
         <v>309</v>
       </c>
-      <c r="G101" s="15"/>
-      <c r="H101" s="15"/>
+      <c r="G101" s="13"/>
+      <c r="H101" s="13"/>
       <c r="I101" s="7">
         <v>3006</v>
       </c>
-      <c r="J101"/>
+      <c r="J101" s="2">
+        <v>3006</v>
+      </c>
       <c r="K101" s="2" t="s">
         <v>12</v>
       </c>
@@ -6032,15 +6184,15 @@
       <c r="R101" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S101" s="36"/>
+      <c r="S101" s="32"/>
       <c r="T101"/>
-      <c r="U101" s="21"/>
+      <c r="U101" s="17"/>
       <c r="V101"/>
       <c r="W101"/>
       <c r="X101"/>
       <c r="Y101"/>
     </row>
-    <row r="102" spans="1:25" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>189</v>
       </c>
@@ -6050,13 +6202,13 @@
       <c r="C102" t="s">
         <v>13</v>
       </c>
-      <c r="D102" s="12"/>
+      <c r="D102"/>
       <c r="E102"/>
-      <c r="F102" s="39" t="s">
+      <c r="F102" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="G102" s="15"/>
-      <c r="H102" s="15"/>
+      <c r="G102" s="13"/>
+      <c r="H102" s="13"/>
       <c r="I102" s="7">
         <v>3006</v>
       </c>
@@ -6077,11 +6229,11 @@
       <c r="R102" t="s">
         <v>13</v>
       </c>
-      <c r="S102" s="35" t="s">
+      <c r="S102" s="31" t="s">
         <v>83</v>
       </c>
       <c r="T102"/>
-      <c r="U102" s="21"/>
+      <c r="U102" s="17"/>
       <c r="V102"/>
       <c r="W102"/>
       <c r="X102"/>
@@ -6097,17 +6249,19 @@
       <c r="C103" t="s">
         <v>13</v>
       </c>
-      <c r="D103" s="12"/>
+      <c r="D103"/>
       <c r="E103"/>
-      <c r="F103" s="39" t="s">
+      <c r="F103" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="G103" s="15"/>
-      <c r="H103" s="15"/>
+      <c r="G103" s="13"/>
+      <c r="H103" s="13"/>
       <c r="I103" s="7">
         <v>3006</v>
       </c>
-      <c r="J103"/>
+      <c r="J103" s="2">
+        <v>3006</v>
+      </c>
       <c r="K103" s="2" t="s">
         <v>12</v>
       </c>
@@ -6124,9 +6278,9 @@
       <c r="R103" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S103" s="36"/>
+      <c r="S103" s="32"/>
       <c r="T103"/>
-      <c r="U103" s="21"/>
+      <c r="U103" s="17"/>
       <c r="V103"/>
       <c r="W103"/>
       <c r="X103"/>
@@ -6142,17 +6296,19 @@
       <c r="C104" t="s">
         <v>13</v>
       </c>
-      <c r="D104" s="12"/>
+      <c r="D104"/>
       <c r="E104"/>
-      <c r="F104" s="39" t="s">
+      <c r="F104" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="G104" s="15"/>
-      <c r="H104" s="15"/>
+      <c r="G104" s="13"/>
+      <c r="H104" s="13"/>
       <c r="I104" s="7">
         <v>3006</v>
       </c>
-      <c r="J104"/>
+      <c r="J104" s="2">
+        <v>3006</v>
+      </c>
       <c r="K104" s="2" t="s">
         <v>12</v>
       </c>
@@ -6169,9 +6325,9 @@
       <c r="R104" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S104" s="36"/>
+      <c r="S104" s="32"/>
       <c r="T104"/>
-      <c r="U104" s="21"/>
+      <c r="U104" s="17"/>
       <c r="V104"/>
       <c r="W104"/>
       <c r="X104"/>
@@ -6187,17 +6343,19 @@
       <c r="C105" t="s">
         <v>13</v>
       </c>
-      <c r="D105" s="12"/>
+      <c r="D105"/>
       <c r="E105"/>
-      <c r="F105" s="39" t="s">
+      <c r="F105" s="35" t="s">
         <v>312</v>
       </c>
-      <c r="G105" s="15"/>
-      <c r="H105" s="15"/>
+      <c r="G105" s="13"/>
+      <c r="H105" s="13"/>
       <c r="I105" s="7">
         <v>3006</v>
       </c>
-      <c r="J105"/>
+      <c r="J105" s="2">
+        <v>3006</v>
+      </c>
       <c r="K105" s="2" t="s">
         <v>12</v>
       </c>
@@ -6214,15 +6372,15 @@
       <c r="R105" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S105" s="36"/>
+      <c r="S105" s="32"/>
       <c r="T105"/>
-      <c r="U105" s="21"/>
+      <c r="U105" s="17"/>
       <c r="V105"/>
       <c r="W105"/>
       <c r="X105"/>
       <c r="Y105"/>
     </row>
-    <row r="106" spans="1:25" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>193</v>
       </c>
@@ -6232,13 +6390,13 @@
       <c r="C106" t="s">
         <v>13</v>
       </c>
-      <c r="D106" s="12"/>
+      <c r="D106"/>
       <c r="E106"/>
-      <c r="F106" s="39" t="s">
+      <c r="F106" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="G106" s="15"/>
-      <c r="H106" s="15"/>
+      <c r="G106" s="13"/>
+      <c r="H106" s="13"/>
       <c r="I106" s="7">
         <v>3006</v>
       </c>
@@ -6259,11 +6417,11 @@
       <c r="R106" t="s">
         <v>13</v>
       </c>
-      <c r="S106" s="35" t="s">
+      <c r="S106" s="31" t="s">
         <v>83</v>
       </c>
       <c r="T106"/>
-      <c r="U106" s="21"/>
+      <c r="U106" s="17"/>
       <c r="V106"/>
       <c r="W106"/>
       <c r="X106"/>
@@ -6279,17 +6437,19 @@
       <c r="C107" t="s">
         <v>13</v>
       </c>
-      <c r="D107" s="12"/>
+      <c r="D107"/>
       <c r="E107"/>
-      <c r="F107" s="39" t="s">
+      <c r="F107" s="35" t="s">
         <v>313</v>
       </c>
-      <c r="G107" s="15"/>
-      <c r="H107" s="15"/>
+      <c r="G107" s="13"/>
+      <c r="H107" s="13"/>
       <c r="I107" s="7">
         <v>3006</v>
       </c>
-      <c r="J107"/>
+      <c r="J107" s="2">
+        <v>3006</v>
+      </c>
       <c r="K107" s="2" t="s">
         <v>12</v>
       </c>
@@ -6306,9 +6466,9 @@
       <c r="R107" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S107" s="36"/>
+      <c r="S107" s="32"/>
       <c r="T107"/>
-      <c r="U107" s="21"/>
+      <c r="U107" s="17"/>
       <c r="V107"/>
       <c r="W107"/>
       <c r="X107"/>
@@ -6324,19 +6484,21 @@
       <c r="C108" t="s">
         <v>13</v>
       </c>
-      <c r="D108" s="12"/>
+      <c r="D108"/>
       <c r="E108" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="F108" s="39" t="s">
+      <c r="F108" s="35" t="s">
         <v>314</v>
       </c>
-      <c r="G108" s="15"/>
-      <c r="H108" s="15"/>
+      <c r="G108" s="13"/>
+      <c r="H108" s="13"/>
       <c r="I108" s="7">
         <v>3006</v>
       </c>
-      <c r="J108"/>
+      <c r="J108" s="2">
+        <v>3006</v>
+      </c>
       <c r="K108" s="2" t="s">
         <v>12</v>
       </c>
@@ -6353,9 +6515,9 @@
       <c r="R108" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S108" s="36"/>
+      <c r="S108" s="32"/>
       <c r="T108"/>
-      <c r="U108" s="21"/>
+      <c r="U108" s="17"/>
       <c r="V108"/>
       <c r="W108"/>
       <c r="X108"/>
@@ -6371,17 +6533,19 @@
       <c r="C109" t="s">
         <v>13</v>
       </c>
-      <c r="D109" s="12"/>
+      <c r="D109"/>
       <c r="E109"/>
-      <c r="F109" s="39" t="s">
+      <c r="F109" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="G109" s="15"/>
-      <c r="H109" s="15"/>
+      <c r="G109" s="13"/>
+      <c r="H109" s="13"/>
       <c r="I109" s="7">
         <v>3006</v>
       </c>
-      <c r="J109"/>
+      <c r="J109" s="2">
+        <v>3006</v>
+      </c>
       <c r="K109" s="2" t="s">
         <v>12</v>
       </c>
@@ -6398,9 +6562,9 @@
       <c r="R109" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S109" s="36"/>
+      <c r="S109" s="32"/>
       <c r="T109"/>
-      <c r="U109" s="21"/>
+      <c r="U109" s="17"/>
       <c r="V109"/>
       <c r="W109"/>
       <c r="X109"/>
@@ -6416,17 +6580,19 @@
       <c r="C110" t="s">
         <v>13</v>
       </c>
-      <c r="D110" s="12"/>
+      <c r="D110"/>
       <c r="E110"/>
-      <c r="F110" s="39" t="s">
+      <c r="F110" s="35" t="s">
         <v>316</v>
       </c>
-      <c r="G110" s="15"/>
-      <c r="H110" s="15"/>
+      <c r="G110" s="13"/>
+      <c r="H110" s="13"/>
       <c r="I110" s="7">
         <v>3006</v>
       </c>
-      <c r="J110"/>
+      <c r="J110" s="2">
+        <v>3006</v>
+      </c>
       <c r="K110" s="2" t="s">
         <v>12</v>
       </c>
@@ -6443,9 +6609,9 @@
       <c r="R110" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S110" s="36"/>
+      <c r="S110" s="32"/>
       <c r="T110"/>
-      <c r="U110" s="21"/>
+      <c r="U110" s="17"/>
       <c r="V110"/>
       <c r="W110"/>
       <c r="X110"/>
@@ -6461,17 +6627,19 @@
       <c r="C111" t="s">
         <v>13</v>
       </c>
-      <c r="D111" s="12"/>
+      <c r="D111"/>
       <c r="E111"/>
-      <c r="F111" s="39" t="s">
+      <c r="F111" s="35" t="s">
         <v>317</v>
       </c>
-      <c r="G111" s="15"/>
-      <c r="H111" s="15"/>
+      <c r="G111" s="13"/>
+      <c r="H111" s="13"/>
       <c r="I111" s="7">
         <v>3006</v>
       </c>
-      <c r="J111"/>
+      <c r="J111" s="2">
+        <v>3006</v>
+      </c>
       <c r="K111" s="2" t="s">
         <v>12</v>
       </c>
@@ -6488,9 +6656,9 @@
       <c r="R111" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S111" s="36"/>
+      <c r="S111" s="32"/>
       <c r="T111"/>
-      <c r="U111" s="21"/>
+      <c r="U111" s="17"/>
       <c r="V111"/>
       <c r="W111"/>
       <c r="X111"/>
@@ -6506,17 +6674,19 @@
       <c r="C112" t="s">
         <v>13</v>
       </c>
-      <c r="D112" s="12"/>
+      <c r="D112"/>
       <c r="E112"/>
-      <c r="F112" s="40" t="s">
+      <c r="F112" s="36" t="s">
         <v>238</v>
       </c>
-      <c r="G112" s="16"/>
-      <c r="H112" s="16"/>
+      <c r="G112"/>
+      <c r="H112"/>
       <c r="I112" s="7">
         <v>3006</v>
       </c>
-      <c r="J112"/>
+      <c r="J112" s="2">
+        <v>3006</v>
+      </c>
       <c r="K112" s="2" t="s">
         <v>12</v>
       </c>
@@ -6533,9 +6703,9 @@
       <c r="R112" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S112" s="36"/>
+      <c r="S112" s="32"/>
       <c r="T112"/>
-      <c r="U112" s="21"/>
+      <c r="U112" s="17"/>
       <c r="V112"/>
       <c r="W112"/>
       <c r="X112"/>
@@ -6551,17 +6721,19 @@
       <c r="C113" t="s">
         <v>13</v>
       </c>
-      <c r="D113" s="12"/>
+      <c r="D113"/>
       <c r="E113"/>
-      <c r="F113" s="39" t="s">
+      <c r="F113" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="G113" s="15"/>
-      <c r="H113" s="15"/>
+      <c r="G113" s="13"/>
+      <c r="H113" s="13"/>
       <c r="I113" s="7">
         <v>3006</v>
       </c>
-      <c r="J113"/>
+      <c r="J113" s="2">
+        <v>3006</v>
+      </c>
       <c r="K113" s="2" t="s">
         <v>12</v>
       </c>
@@ -6578,9 +6750,9 @@
       <c r="R113" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S113" s="36"/>
+      <c r="S113" s="32"/>
       <c r="T113"/>
-      <c r="U113" s="21"/>
+      <c r="U113" s="17"/>
       <c r="V113"/>
       <c r="W113"/>
       <c r="X113"/>
@@ -6596,17 +6768,19 @@
       <c r="C114" t="s">
         <v>13</v>
       </c>
-      <c r="D114" s="12"/>
+      <c r="D114"/>
       <c r="E114"/>
-      <c r="F114" s="39" t="s">
+      <c r="F114" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="G114" s="15"/>
-      <c r="H114" s="15"/>
+      <c r="G114" s="13"/>
+      <c r="H114" s="13"/>
       <c r="I114" s="7">
         <v>3006</v>
       </c>
-      <c r="J114"/>
+      <c r="J114" s="2">
+        <v>3006</v>
+      </c>
       <c r="K114" s="2" t="s">
         <v>12</v>
       </c>
@@ -6623,9 +6797,9 @@
       <c r="R114" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S114" s="36"/>
+      <c r="S114" s="32"/>
       <c r="T114"/>
-      <c r="U114" s="21"/>
+      <c r="U114" s="17"/>
       <c r="V114"/>
       <c r="W114"/>
       <c r="X114"/>
@@ -6641,17 +6815,19 @@
       <c r="C115" t="s">
         <v>13</v>
       </c>
-      <c r="D115" s="12"/>
+      <c r="D115"/>
       <c r="E115"/>
-      <c r="F115" s="39" t="s">
+      <c r="F115" s="35" t="s">
         <v>320</v>
       </c>
-      <c r="G115" s="15"/>
-      <c r="H115" s="15"/>
+      <c r="G115" s="13"/>
+      <c r="H115" s="13"/>
       <c r="I115" s="7">
         <v>3006</v>
       </c>
-      <c r="J115"/>
+      <c r="J115" s="2">
+        <v>3006</v>
+      </c>
       <c r="K115" s="2" t="s">
         <v>12</v>
       </c>
@@ -6668,9 +6844,9 @@
       <c r="R115" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S115" s="36"/>
+      <c r="S115" s="32"/>
       <c r="T115"/>
-      <c r="U115" s="21"/>
+      <c r="U115" s="17"/>
       <c r="V115"/>
       <c r="W115"/>
       <c r="X115"/>
@@ -6686,17 +6862,19 @@
       <c r="C116" t="s">
         <v>13</v>
       </c>
-      <c r="D116" s="12"/>
+      <c r="D116"/>
       <c r="E116"/>
-      <c r="F116" s="39" t="s">
+      <c r="F116" s="35" t="s">
         <v>321</v>
       </c>
-      <c r="G116" s="15"/>
-      <c r="H116" s="15"/>
+      <c r="G116" s="13"/>
+      <c r="H116" s="13"/>
       <c r="I116" s="7">
         <v>3006</v>
       </c>
-      <c r="J116"/>
+      <c r="J116" s="2">
+        <v>3006</v>
+      </c>
       <c r="K116" s="2" t="s">
         <v>12</v>
       </c>
@@ -6713,9 +6891,9 @@
       <c r="R116" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S116" s="36"/>
+      <c r="S116" s="32"/>
       <c r="T116"/>
-      <c r="U116" s="21"/>
+      <c r="U116" s="17"/>
       <c r="V116"/>
       <c r="W116"/>
       <c r="X116"/>
@@ -6731,17 +6909,19 @@
       <c r="C117" t="s">
         <v>13</v>
       </c>
-      <c r="D117" s="12"/>
+      <c r="D117"/>
       <c r="E117"/>
-      <c r="F117" s="39" t="s">
+      <c r="F117" s="35" t="s">
         <v>322</v>
       </c>
-      <c r="G117" s="15"/>
-      <c r="H117" s="15"/>
+      <c r="G117" s="13"/>
+      <c r="H117" s="13"/>
       <c r="I117" s="7">
         <v>3006</v>
       </c>
-      <c r="J117"/>
+      <c r="J117" s="2">
+        <v>3006</v>
+      </c>
       <c r="K117" s="2" t="s">
         <v>12</v>
       </c>
@@ -6758,9 +6938,9 @@
       <c r="R117" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S117" s="36"/>
+      <c r="S117" s="32"/>
       <c r="T117"/>
-      <c r="U117" s="21"/>
+      <c r="U117" s="17"/>
       <c r="V117"/>
       <c r="W117"/>
       <c r="X117"/>
@@ -6776,17 +6956,19 @@
       <c r="C118" t="s">
         <v>13</v>
       </c>
-      <c r="D118" s="12"/>
+      <c r="D118"/>
       <c r="E118"/>
-      <c r="F118" s="39" t="s">
+      <c r="F118" s="35" t="s">
         <v>323</v>
       </c>
-      <c r="G118" s="15"/>
-      <c r="H118" s="15"/>
+      <c r="G118" s="13"/>
+      <c r="H118" s="13"/>
       <c r="I118" s="7">
         <v>3006</v>
       </c>
-      <c r="J118"/>
+      <c r="J118" s="2">
+        <v>3006</v>
+      </c>
       <c r="K118" s="2" t="s">
         <v>12</v>
       </c>
@@ -6803,9 +6985,9 @@
       <c r="R118" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S118" s="36"/>
+      <c r="S118" s="32"/>
       <c r="T118"/>
-      <c r="U118" s="21"/>
+      <c r="U118" s="17"/>
       <c r="V118"/>
       <c r="W118"/>
       <c r="X118"/>
@@ -6821,17 +7003,19 @@
       <c r="C119" t="s">
         <v>13</v>
       </c>
-      <c r="D119" s="12"/>
+      <c r="D119"/>
       <c r="E119"/>
-      <c r="F119" s="39" t="s">
+      <c r="F119" s="35" t="s">
         <v>324</v>
       </c>
-      <c r="G119" s="15"/>
-      <c r="H119" s="15"/>
+      <c r="G119" s="13"/>
+      <c r="H119" s="13"/>
       <c r="I119" s="7">
         <v>3006</v>
       </c>
-      <c r="J119"/>
+      <c r="J119" s="2">
+        <v>3006</v>
+      </c>
       <c r="K119" s="2" t="s">
         <v>12</v>
       </c>
@@ -6848,9 +7032,9 @@
       <c r="R119" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S119" s="36"/>
+      <c r="S119" s="32"/>
       <c r="T119"/>
-      <c r="U119" s="21"/>
+      <c r="U119" s="17"/>
       <c r="V119"/>
       <c r="W119"/>
       <c r="X119"/>
@@ -6866,17 +7050,19 @@
       <c r="C120" t="s">
         <v>13</v>
       </c>
-      <c r="D120" s="12"/>
+      <c r="D120"/>
       <c r="E120"/>
-      <c r="F120" s="39" t="s">
+      <c r="F120" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="G120" s="15"/>
-      <c r="H120" s="15"/>
+      <c r="G120" s="13"/>
+      <c r="H120" s="13"/>
       <c r="I120" s="7">
         <v>3006</v>
       </c>
-      <c r="J120"/>
+      <c r="J120" s="2">
+        <v>3006</v>
+      </c>
       <c r="K120" s="2" t="s">
         <v>12</v>
       </c>
@@ -6893,9 +7079,9 @@
       <c r="R120" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S120" s="36"/>
+      <c r="S120" s="32"/>
       <c r="T120"/>
-      <c r="U120" s="21"/>
+      <c r="U120" s="17"/>
       <c r="V120"/>
       <c r="W120"/>
       <c r="X120"/>
@@ -6911,17 +7097,19 @@
       <c r="C121" t="s">
         <v>13</v>
       </c>
-      <c r="D121" s="12"/>
+      <c r="D121"/>
       <c r="E121"/>
-      <c r="F121" s="39" t="s">
+      <c r="F121" s="35" t="s">
         <v>326</v>
       </c>
-      <c r="G121" s="15"/>
-      <c r="H121" s="15"/>
+      <c r="G121" s="13"/>
+      <c r="H121" s="13"/>
       <c r="I121" s="7">
         <v>3006</v>
       </c>
-      <c r="J121"/>
+      <c r="J121" s="2">
+        <v>3006</v>
+      </c>
       <c r="K121" s="2" t="s">
         <v>12</v>
       </c>
@@ -6938,9 +7126,9 @@
       <c r="R121" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S121" s="36"/>
+      <c r="S121" s="32"/>
       <c r="T121"/>
-      <c r="U121" s="21"/>
+      <c r="U121" s="17"/>
       <c r="V121"/>
       <c r="W121"/>
       <c r="X121"/>
@@ -6956,17 +7144,19 @@
       <c r="C122" t="s">
         <v>13</v>
       </c>
-      <c r="D122" s="12"/>
+      <c r="D122"/>
       <c r="E122"/>
-      <c r="F122" s="39" t="s">
+      <c r="F122" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="G122" s="15"/>
-      <c r="H122" s="15"/>
+      <c r="G122" s="13"/>
+      <c r="H122" s="13"/>
       <c r="I122" s="7">
         <v>3006</v>
       </c>
-      <c r="J122"/>
+      <c r="J122" s="2">
+        <v>3006</v>
+      </c>
       <c r="K122" s="2" t="s">
         <v>12</v>
       </c>
@@ -6983,9 +7173,9 @@
       <c r="R122" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S122" s="36"/>
+      <c r="S122" s="32"/>
       <c r="T122"/>
-      <c r="U122" s="21"/>
+      <c r="U122" s="17"/>
       <c r="V122"/>
       <c r="W122"/>
       <c r="X122"/>
@@ -7001,17 +7191,19 @@
       <c r="C123" t="s">
         <v>13</v>
       </c>
-      <c r="D123" s="12"/>
+      <c r="D123"/>
       <c r="E123"/>
-      <c r="F123" s="39" t="s">
+      <c r="F123" s="35" t="s">
         <v>328</v>
       </c>
-      <c r="G123" s="15"/>
-      <c r="H123" s="15"/>
+      <c r="G123" s="13"/>
+      <c r="H123" s="13"/>
       <c r="I123" s="7">
         <v>3006</v>
       </c>
-      <c r="J123"/>
+      <c r="J123" s="2">
+        <v>3006</v>
+      </c>
       <c r="K123" s="2" t="s">
         <v>12</v>
       </c>
@@ -7028,9 +7220,9 @@
       <c r="R123" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S123" s="36"/>
+      <c r="S123" s="32"/>
       <c r="T123"/>
-      <c r="U123" s="21"/>
+      <c r="U123" s="17"/>
       <c r="V123"/>
       <c r="W123"/>
       <c r="X123"/>
@@ -7046,17 +7238,19 @@
       <c r="C124" t="s">
         <v>13</v>
       </c>
-      <c r="D124" s="12"/>
+      <c r="D124"/>
       <c r="E124"/>
-      <c r="F124" s="39" t="s">
+      <c r="F124" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="G124" s="15"/>
-      <c r="H124" s="15"/>
+      <c r="G124" s="13"/>
+      <c r="H124" s="13"/>
       <c r="I124" s="7">
         <v>3006</v>
       </c>
-      <c r="J124"/>
+      <c r="J124" s="2">
+        <v>3006</v>
+      </c>
       <c r="K124" s="2" t="s">
         <v>12</v>
       </c>
@@ -7073,9 +7267,9 @@
       <c r="R124" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S124" s="36"/>
+      <c r="S124" s="32"/>
       <c r="T124"/>
-      <c r="U124" s="21"/>
+      <c r="U124" s="17"/>
       <c r="V124"/>
       <c r="W124"/>
       <c r="X124"/>
@@ -7091,17 +7285,19 @@
       <c r="C125" t="s">
         <v>13</v>
       </c>
-      <c r="D125" s="12"/>
+      <c r="D125"/>
       <c r="E125"/>
-      <c r="F125" s="39" t="s">
+      <c r="F125" s="35" t="s">
         <v>330</v>
       </c>
-      <c r="G125" s="15"/>
-      <c r="H125" s="15"/>
+      <c r="G125" s="13"/>
+      <c r="H125" s="13"/>
       <c r="I125" s="7">
         <v>3006</v>
       </c>
-      <c r="J125"/>
+      <c r="J125" s="2">
+        <v>3006</v>
+      </c>
       <c r="K125" s="2" t="s">
         <v>12</v>
       </c>
@@ -7118,9 +7314,9 @@
       <c r="R125" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S125" s="36"/>
+      <c r="S125" s="32"/>
       <c r="T125"/>
-      <c r="U125" s="21"/>
+      <c r="U125" s="17"/>
       <c r="V125"/>
       <c r="W125"/>
       <c r="X125"/>
@@ -7136,17 +7332,19 @@
       <c r="C126" t="s">
         <v>13</v>
       </c>
-      <c r="D126" s="12"/>
+      <c r="D126"/>
       <c r="E126"/>
-      <c r="F126" s="39" t="s">
+      <c r="F126" s="35" t="s">
         <v>331</v>
       </c>
-      <c r="G126" s="15"/>
-      <c r="H126" s="15"/>
+      <c r="G126" s="13"/>
+      <c r="H126" s="13"/>
       <c r="I126" s="7">
         <v>3006</v>
       </c>
-      <c r="J126"/>
+      <c r="J126" s="2">
+        <v>3006</v>
+      </c>
       <c r="K126" s="2" t="s">
         <v>12</v>
       </c>
@@ -7163,9 +7361,9 @@
       <c r="R126" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S126" s="36"/>
+      <c r="S126" s="32"/>
       <c r="T126"/>
-      <c r="U126" s="21"/>
+      <c r="U126" s="17"/>
       <c r="V126"/>
       <c r="W126"/>
       <c r="X126"/>
@@ -7181,17 +7379,19 @@
       <c r="C127" t="s">
         <v>13</v>
       </c>
-      <c r="D127" s="12"/>
+      <c r="D127"/>
       <c r="E127"/>
-      <c r="F127" s="39" t="s">
+      <c r="F127" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="G127" s="15"/>
-      <c r="H127" s="15"/>
+      <c r="G127" s="13"/>
+      <c r="H127" s="13"/>
       <c r="I127" s="7">
         <v>3006</v>
       </c>
-      <c r="J127"/>
+      <c r="J127" s="2">
+        <v>3006</v>
+      </c>
       <c r="K127" s="2" t="s">
         <v>12</v>
       </c>
@@ -7208,1147 +7408,1133 @@
       <c r="R127" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="S127" s="36"/>
+      <c r="S127" s="32"/>
       <c r="T127"/>
-      <c r="U127" s="21"/>
+      <c r="U127" s="17"/>
       <c r="V127"/>
       <c r="W127"/>
       <c r="X127"/>
       <c r="Y127"/>
     </row>
-    <row r="128" spans="1:25" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="12" t="s">
+    <row r="128" spans="1:25" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
         <v>215</v>
       </c>
       <c r="B128" t="s">
         <v>15</v>
       </c>
-      <c r="C128" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D128" s="12" t="s">
+      <c r="C128" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128" t="s">
         <v>56</v>
       </c>
-      <c r="F128" s="39"/>
-      <c r="G128" s="15"/>
-      <c r="H128" s="15"/>
+      <c r="F128" s="35"/>
+      <c r="G128" s="13"/>
+      <c r="H128" s="13"/>
       <c r="K128" s="2"/>
       <c r="R128" t="s">
         <v>13</v>
       </c>
-      <c r="S128" s="36" t="s">
+      <c r="S128" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="U128" s="21"/>
-    </row>
-    <row r="129" spans="1:21" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="12" t="s">
+      <c r="U128" s="17"/>
+    </row>
+    <row r="129" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
         <v>216</v>
       </c>
       <c r="B129" t="s">
         <v>15</v>
       </c>
-      <c r="C129" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D129" s="12" t="s">
+      <c r="C129" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129" t="s">
         <v>56</v>
       </c>
-      <c r="F129" s="39"/>
-      <c r="G129" s="15"/>
-      <c r="H129" s="15"/>
+      <c r="F129" s="35"/>
+      <c r="G129" s="13"/>
+      <c r="H129" s="13"/>
       <c r="K129" s="2"/>
       <c r="R129" t="s">
         <v>13</v>
       </c>
-      <c r="S129" s="36" t="s">
+      <c r="S129" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="U129" s="21"/>
-    </row>
-    <row r="130" spans="1:21" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="12" t="s">
+      <c r="U129" s="17"/>
+    </row>
+    <row r="130" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
         <v>217</v>
       </c>
       <c r="B130" t="s">
         <v>15</v>
       </c>
-      <c r="C130" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D130" s="12" t="s">
+      <c r="C130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D130" t="s">
         <v>56</v>
       </c>
-      <c r="F130" s="39"/>
-      <c r="G130" s="15"/>
-      <c r="H130" s="15"/>
+      <c r="F130" s="35"/>
+      <c r="G130" s="13"/>
+      <c r="H130" s="13"/>
       <c r="R130" t="s">
         <v>13</v>
       </c>
-      <c r="S130" s="36" t="s">
+      <c r="S130" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="U130" s="21"/>
+      <c r="U130" s="17"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="12"/>
-      <c r="B131" s="12"/>
-      <c r="C131" s="12"/>
-      <c r="D131" s="12"/>
-      <c r="F131" s="39"/>
-      <c r="G131" s="15"/>
-      <c r="H131" s="15"/>
-      <c r="S131" s="36"/>
-      <c r="U131" s="21"/>
+      <c r="A131"/>
+      <c r="B131"/>
+      <c r="C131"/>
+      <c r="D131"/>
+      <c r="F131" s="35"/>
+      <c r="G131" s="13"/>
+      <c r="H131" s="13"/>
+      <c r="S131" s="32"/>
+      <c r="U131" s="17"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="12"/>
-      <c r="B132" s="12"/>
-      <c r="C132" s="12"/>
-      <c r="D132" s="12"/>
-      <c r="F132" s="39"/>
-      <c r="G132" s="15"/>
-      <c r="H132" s="15"/>
-      <c r="S132" s="36"/>
-      <c r="U132" s="21"/>
+      <c r="A132"/>
+      <c r="B132"/>
+      <c r="C132"/>
+      <c r="D132"/>
+      <c r="F132" s="35"/>
+      <c r="G132" s="13"/>
+      <c r="H132" s="13"/>
+      <c r="S132" s="32"/>
+      <c r="U132" s="17"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="12"/>
-      <c r="B133" s="12"/>
-      <c r="C133" s="12"/>
-      <c r="D133" s="12"/>
-      <c r="F133" s="39"/>
-      <c r="G133" s="15"/>
-      <c r="H133" s="15"/>
-      <c r="S133" s="36"/>
-      <c r="U133" s="21"/>
+      <c r="A133"/>
+      <c r="B133"/>
+      <c r="C133"/>
+      <c r="D133"/>
+      <c r="F133" s="35"/>
+      <c r="G133" s="13"/>
+      <c r="H133" s="13"/>
+      <c r="S133" s="32"/>
+      <c r="U133" s="17"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="12"/>
-      <c r="B134" s="12"/>
-      <c r="C134" s="12"/>
-      <c r="D134" s="12"/>
-      <c r="F134" s="39"/>
-      <c r="G134" s="15"/>
-      <c r="H134" s="15"/>
-      <c r="S134" s="36"/>
-      <c r="U134" s="21"/>
+      <c r="A134"/>
+      <c r="B134"/>
+      <c r="C134"/>
+      <c r="D134"/>
+      <c r="F134" s="35"/>
+      <c r="G134" s="13"/>
+      <c r="H134" s="13"/>
+      <c r="S134" s="32"/>
+      <c r="U134" s="17"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="12"/>
-      <c r="B135" s="12"/>
-      <c r="C135" s="12"/>
-      <c r="D135" s="12"/>
-      <c r="F135" s="39"/>
-      <c r="G135" s="15"/>
-      <c r="H135" s="15"/>
-      <c r="S135" s="36"/>
-      <c r="U135" s="21"/>
+      <c r="A135"/>
+      <c r="B135"/>
+      <c r="C135"/>
+      <c r="D135"/>
+      <c r="F135" s="35"/>
+      <c r="G135" s="13"/>
+      <c r="H135" s="13"/>
+      <c r="S135" s="32"/>
+      <c r="U135" s="17"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="12"/>
-      <c r="B136" s="12"/>
-      <c r="C136" s="12"/>
-      <c r="D136" s="12"/>
-      <c r="F136" s="39"/>
-      <c r="G136" s="15"/>
-      <c r="H136" s="15"/>
-      <c r="S136" s="36"/>
-      <c r="U136" s="21"/>
+      <c r="A136"/>
+      <c r="B136"/>
+      <c r="C136"/>
+      <c r="D136"/>
+      <c r="F136" s="35"/>
+      <c r="G136" s="13"/>
+      <c r="H136" s="13"/>
+      <c r="S136" s="32"/>
+      <c r="U136" s="17"/>
     </row>
     <row r="137" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="12"/>
-      <c r="B137" s="12"/>
-      <c r="C137" s="12"/>
-      <c r="D137" s="12"/>
-      <c r="F137" s="39"/>
-      <c r="G137" s="15"/>
-      <c r="H137" s="15"/>
-      <c r="S137" s="36"/>
-      <c r="U137" s="21"/>
+      <c r="A137"/>
+      <c r="B137"/>
+      <c r="C137"/>
+      <c r="D137"/>
+      <c r="F137" s="35"/>
+      <c r="G137" s="13"/>
+      <c r="H137" s="13"/>
+      <c r="S137" s="32"/>
+      <c r="U137" s="17"/>
     </row>
     <row r="138" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="12"/>
-      <c r="B138" s="12"/>
-      <c r="C138" s="12"/>
-      <c r="D138" s="12"/>
-      <c r="F138" s="39"/>
-      <c r="G138" s="15"/>
-      <c r="H138" s="15"/>
-      <c r="S138" s="36"/>
-      <c r="U138" s="21"/>
+      <c r="A138"/>
+      <c r="B138"/>
+      <c r="C138"/>
+      <c r="D138"/>
+      <c r="F138" s="35"/>
+      <c r="G138" s="13"/>
+      <c r="H138" s="13"/>
+      <c r="S138" s="32"/>
+      <c r="U138" s="17"/>
     </row>
     <row r="139" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="12"/>
-      <c r="B139" s="12"/>
-      <c r="C139" s="12"/>
-      <c r="D139" s="12"/>
-      <c r="F139" s="39"/>
-      <c r="G139" s="15"/>
-      <c r="H139" s="15"/>
-      <c r="S139" s="36"/>
-      <c r="U139" s="21"/>
+      <c r="A139"/>
+      <c r="B139"/>
+      <c r="C139"/>
+      <c r="D139"/>
+      <c r="F139" s="35"/>
+      <c r="G139" s="13"/>
+      <c r="H139" s="13"/>
+      <c r="S139" s="32"/>
+      <c r="U139" s="17"/>
     </row>
     <row r="140" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="12"/>
-      <c r="B140" s="12"/>
-      <c r="C140" s="12"/>
-      <c r="D140" s="12"/>
-      <c r="F140" s="39"/>
-      <c r="G140" s="15"/>
-      <c r="H140" s="15"/>
-      <c r="S140" s="36"/>
-      <c r="U140" s="21"/>
+      <c r="A140"/>
+      <c r="B140"/>
+      <c r="C140"/>
+      <c r="D140"/>
+      <c r="F140" s="35"/>
+      <c r="G140" s="13"/>
+      <c r="H140" s="13"/>
+      <c r="S140" s="32"/>
+      <c r="U140" s="17"/>
     </row>
     <row r="141" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="12"/>
-      <c r="B141" s="12"/>
-      <c r="C141" s="12"/>
-      <c r="D141" s="12"/>
-      <c r="F141" s="39"/>
-      <c r="G141" s="15"/>
-      <c r="H141" s="15"/>
-      <c r="S141" s="36"/>
-      <c r="U141" s="21"/>
+      <c r="A141"/>
+      <c r="B141"/>
+      <c r="C141"/>
+      <c r="D141"/>
+      <c r="F141" s="35"/>
+      <c r="G141" s="13"/>
+      <c r="H141" s="13"/>
+      <c r="S141" s="32"/>
+      <c r="U141" s="17"/>
     </row>
     <row r="142" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="12"/>
-      <c r="B142" s="12"/>
-      <c r="C142" s="12"/>
-      <c r="D142" s="12"/>
-      <c r="F142" s="39"/>
-      <c r="G142" s="15"/>
-      <c r="H142" s="15"/>
-      <c r="S142" s="36"/>
-      <c r="U142" s="21"/>
+      <c r="A142"/>
+      <c r="B142"/>
+      <c r="C142"/>
+      <c r="D142"/>
+      <c r="F142" s="35"/>
+      <c r="G142" s="13"/>
+      <c r="H142" s="13"/>
+      <c r="S142" s="32"/>
+      <c r="U142" s="17"/>
     </row>
     <row r="143" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="12"/>
-      <c r="B143" s="12"/>
-      <c r="C143" s="12"/>
-      <c r="D143" s="12"/>
-      <c r="F143" s="39"/>
-      <c r="G143" s="15"/>
-      <c r="H143" s="15"/>
-      <c r="S143" s="36"/>
-      <c r="U143" s="21"/>
+      <c r="A143"/>
+      <c r="B143"/>
+      <c r="C143"/>
+      <c r="D143"/>
+      <c r="F143" s="35"/>
+      <c r="G143" s="13"/>
+      <c r="H143" s="13"/>
+      <c r="S143" s="32"/>
+      <c r="U143" s="17"/>
     </row>
     <row r="144" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="12"/>
-      <c r="B144" s="12"/>
-      <c r="C144" s="12"/>
-      <c r="D144" s="12"/>
-      <c r="F144" s="39"/>
-      <c r="G144" s="15"/>
-      <c r="H144" s="15"/>
-      <c r="S144" s="36"/>
-      <c r="U144" s="21"/>
+      <c r="A144"/>
+      <c r="B144"/>
+      <c r="C144"/>
+      <c r="D144"/>
+      <c r="F144" s="35"/>
+      <c r="G144" s="13"/>
+      <c r="H144" s="13"/>
+      <c r="S144" s="32"/>
+      <c r="U144" s="17"/>
     </row>
     <row r="145" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="12"/>
-      <c r="B145" s="12"/>
-      <c r="C145" s="12"/>
-      <c r="D145" s="12"/>
-      <c r="F145" s="39"/>
-      <c r="G145" s="15"/>
-      <c r="H145" s="15"/>
-      <c r="S145" s="36"/>
-      <c r="U145" s="21"/>
+      <c r="A145"/>
+      <c r="B145"/>
+      <c r="C145"/>
+      <c r="D145"/>
+      <c r="F145" s="35"/>
+      <c r="G145" s="13"/>
+      <c r="H145" s="13"/>
+      <c r="S145" s="32"/>
+      <c r="U145" s="17"/>
     </row>
     <row r="146" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="12"/>
-      <c r="B146" s="12"/>
-      <c r="C146" s="12"/>
-      <c r="D146" s="12"/>
-      <c r="F146" s="39"/>
-      <c r="G146" s="15"/>
-      <c r="H146" s="15"/>
-      <c r="S146" s="36"/>
-      <c r="U146" s="21"/>
+      <c r="A146"/>
+      <c r="B146"/>
+      <c r="C146"/>
+      <c r="D146"/>
+      <c r="F146" s="35"/>
+      <c r="G146" s="13"/>
+      <c r="H146" s="13"/>
+      <c r="S146" s="32"/>
+      <c r="U146" s="17"/>
     </row>
     <row r="147" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="12"/>
-      <c r="B147" s="12"/>
-      <c r="C147" s="12"/>
-      <c r="D147" s="12"/>
-      <c r="F147" s="39"/>
-      <c r="G147" s="15"/>
-      <c r="H147" s="15"/>
-      <c r="S147" s="36"/>
-      <c r="U147" s="21"/>
+      <c r="A147"/>
+      <c r="B147"/>
+      <c r="C147"/>
+      <c r="D147"/>
+      <c r="F147" s="35"/>
+      <c r="G147" s="13"/>
+      <c r="H147" s="13"/>
+      <c r="S147" s="32"/>
+      <c r="U147" s="17"/>
     </row>
     <row r="148" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="12"/>
-      <c r="B148" s="12"/>
-      <c r="C148" s="12"/>
-      <c r="D148" s="12"/>
-      <c r="F148" s="39"/>
-      <c r="G148" s="15"/>
-      <c r="H148" s="15"/>
-      <c r="S148" s="36"/>
-      <c r="U148" s="21"/>
+      <c r="A148"/>
+      <c r="B148"/>
+      <c r="C148"/>
+      <c r="D148"/>
+      <c r="F148" s="35"/>
+      <c r="G148" s="13"/>
+      <c r="H148" s="13"/>
+      <c r="S148" s="32"/>
+      <c r="U148" s="17"/>
     </row>
     <row r="149" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="12"/>
-      <c r="B149" s="12"/>
-      <c r="C149" s="12"/>
-      <c r="D149" s="12"/>
-      <c r="F149" s="39"/>
-      <c r="G149" s="15"/>
-      <c r="H149" s="15"/>
-      <c r="S149" s="36"/>
-      <c r="U149" s="21"/>
+      <c r="A149"/>
+      <c r="B149"/>
+      <c r="C149"/>
+      <c r="D149"/>
+      <c r="F149" s="35"/>
+      <c r="G149" s="13"/>
+      <c r="H149" s="13"/>
+      <c r="S149" s="32"/>
+      <c r="U149" s="17"/>
     </row>
     <row r="150" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="12"/>
-      <c r="B150" s="12"/>
-      <c r="C150" s="12"/>
-      <c r="D150" s="12"/>
-      <c r="F150" s="39"/>
-      <c r="G150" s="15"/>
-      <c r="H150" s="15"/>
-      <c r="S150" s="36"/>
-      <c r="U150" s="21"/>
+      <c r="A150"/>
+      <c r="B150"/>
+      <c r="C150"/>
+      <c r="D150"/>
+      <c r="F150" s="35"/>
+      <c r="G150" s="13"/>
+      <c r="H150" s="13"/>
+      <c r="S150" s="32"/>
+      <c r="U150" s="17"/>
     </row>
     <row r="151" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="12"/>
-      <c r="B151" s="12"/>
-      <c r="C151" s="12"/>
-      <c r="D151" s="12"/>
-      <c r="F151" s="39"/>
-      <c r="G151" s="15"/>
-      <c r="H151" s="15"/>
-      <c r="S151" s="36"/>
-      <c r="U151" s="21"/>
+      <c r="A151"/>
+      <c r="B151"/>
+      <c r="C151"/>
+      <c r="D151"/>
+      <c r="F151" s="35"/>
+      <c r="G151" s="13"/>
+      <c r="H151" s="13"/>
+      <c r="S151" s="32"/>
+      <c r="U151" s="17"/>
     </row>
     <row r="152" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="12"/>
-      <c r="B152" s="12"/>
-      <c r="C152" s="12"/>
-      <c r="D152" s="12"/>
-      <c r="F152" s="39"/>
-      <c r="G152" s="15"/>
-      <c r="H152" s="15"/>
-      <c r="S152" s="36"/>
-      <c r="U152" s="21"/>
+      <c r="A152"/>
+      <c r="B152"/>
+      <c r="C152"/>
+      <c r="D152"/>
+      <c r="F152" s="35"/>
+      <c r="G152" s="13"/>
+      <c r="H152" s="13"/>
+      <c r="S152" s="32"/>
+      <c r="U152" s="17"/>
     </row>
     <row r="153" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="12"/>
-      <c r="B153" s="12"/>
-      <c r="C153" s="12"/>
-      <c r="D153" s="12"/>
-      <c r="F153" s="39"/>
-      <c r="G153" s="15"/>
-      <c r="H153" s="15"/>
-      <c r="S153" s="36"/>
-      <c r="U153" s="21"/>
+      <c r="A153"/>
+      <c r="B153"/>
+      <c r="C153"/>
+      <c r="D153"/>
+      <c r="F153" s="35"/>
+      <c r="G153" s="13"/>
+      <c r="H153" s="13"/>
+      <c r="S153" s="32"/>
+      <c r="U153" s="17"/>
     </row>
     <row r="154" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="12"/>
-      <c r="B154" s="12"/>
-      <c r="C154" s="12"/>
-      <c r="D154" s="12"/>
-      <c r="F154" s="39"/>
-      <c r="G154" s="15"/>
-      <c r="H154" s="15"/>
-      <c r="S154" s="36"/>
-      <c r="U154" s="21"/>
+      <c r="A154"/>
+      <c r="B154"/>
+      <c r="C154"/>
+      <c r="D154"/>
+      <c r="F154" s="35"/>
+      <c r="G154" s="13"/>
+      <c r="H154" s="13"/>
+      <c r="S154" s="32"/>
+      <c r="U154" s="17"/>
     </row>
     <row r="155" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="12"/>
-      <c r="B155" s="12"/>
-      <c r="C155" s="12"/>
-      <c r="D155" s="12"/>
-      <c r="F155" s="39"/>
-      <c r="G155" s="15"/>
-      <c r="H155" s="15"/>
-      <c r="S155" s="36"/>
-      <c r="U155" s="21"/>
+      <c r="A155"/>
+      <c r="B155"/>
+      <c r="C155"/>
+      <c r="D155"/>
+      <c r="F155" s="35"/>
+      <c r="G155" s="13"/>
+      <c r="H155" s="13"/>
+      <c r="S155" s="32"/>
+      <c r="U155" s="17"/>
     </row>
     <row r="156" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="12"/>
-      <c r="B156" s="12"/>
-      <c r="C156" s="12"/>
-      <c r="D156" s="12"/>
-      <c r="F156" s="39"/>
-      <c r="G156" s="15"/>
-      <c r="H156" s="15"/>
-      <c r="S156" s="36"/>
-      <c r="U156" s="21"/>
+      <c r="A156"/>
+      <c r="B156"/>
+      <c r="C156"/>
+      <c r="D156"/>
+      <c r="F156" s="35"/>
+      <c r="G156" s="13"/>
+      <c r="H156" s="13"/>
+      <c r="S156" s="32"/>
+      <c r="U156" s="17"/>
     </row>
     <row r="157" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="12"/>
-      <c r="B157" s="12"/>
-      <c r="C157" s="12"/>
-      <c r="D157" s="12"/>
-      <c r="F157" s="39"/>
-      <c r="G157" s="15"/>
-      <c r="H157" s="15"/>
-      <c r="S157" s="36"/>
-      <c r="U157" s="21"/>
+      <c r="A157"/>
+      <c r="B157"/>
+      <c r="C157"/>
+      <c r="D157"/>
+      <c r="F157" s="35"/>
+      <c r="G157" s="13"/>
+      <c r="H157" s="13"/>
+      <c r="S157" s="32"/>
+      <c r="U157" s="17"/>
     </row>
     <row r="158" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="12"/>
-      <c r="B158" s="12"/>
-      <c r="C158" s="12"/>
-      <c r="D158" s="12"/>
-      <c r="F158" s="39"/>
-      <c r="G158" s="15"/>
-      <c r="H158" s="15"/>
-      <c r="S158" s="36"/>
-      <c r="U158" s="21"/>
+      <c r="A158"/>
+      <c r="B158"/>
+      <c r="C158"/>
+      <c r="D158"/>
+      <c r="F158" s="35"/>
+      <c r="G158" s="13"/>
+      <c r="H158" s="13"/>
+      <c r="S158" s="32"/>
+      <c r="U158" s="17"/>
     </row>
     <row r="159" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="12"/>
-      <c r="B159" s="12"/>
-      <c r="C159" s="12"/>
-      <c r="D159" s="12"/>
-      <c r="F159" s="39"/>
-      <c r="G159" s="15"/>
-      <c r="H159" s="15"/>
-      <c r="S159" s="36"/>
-      <c r="U159" s="21"/>
+      <c r="A159"/>
+      <c r="B159"/>
+      <c r="C159"/>
+      <c r="D159"/>
+      <c r="F159" s="35"/>
+      <c r="G159" s="13"/>
+      <c r="H159" s="13"/>
+      <c r="S159" s="32"/>
+      <c r="U159" s="17"/>
     </row>
     <row r="160" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="12"/>
-      <c r="B160" s="12"/>
-      <c r="C160" s="12"/>
-      <c r="D160" s="12"/>
-      <c r="F160" s="39"/>
-      <c r="G160" s="15"/>
-      <c r="H160" s="15"/>
-      <c r="S160" s="36"/>
-      <c r="U160" s="21"/>
+      <c r="A160"/>
+      <c r="B160"/>
+      <c r="C160"/>
+      <c r="D160"/>
+      <c r="F160" s="35"/>
+      <c r="G160" s="13"/>
+      <c r="H160" s="13"/>
+      <c r="S160" s="32"/>
+      <c r="U160" s="17"/>
     </row>
     <row r="161" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="12"/>
-      <c r="B161" s="12"/>
-      <c r="C161" s="12"/>
-      <c r="D161" s="12"/>
-      <c r="F161" s="39"/>
-      <c r="G161" s="15"/>
-      <c r="H161" s="15"/>
-      <c r="S161" s="36"/>
-      <c r="U161" s="21"/>
+      <c r="A161"/>
+      <c r="B161"/>
+      <c r="C161"/>
+      <c r="D161"/>
+      <c r="F161" s="35"/>
+      <c r="G161" s="13"/>
+      <c r="H161" s="13"/>
+      <c r="S161" s="32"/>
+      <c r="U161" s="17"/>
     </row>
     <row r="162" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="12"/>
-      <c r="B162" s="12"/>
-      <c r="C162" s="12"/>
-      <c r="D162" s="12"/>
-      <c r="F162" s="39"/>
-      <c r="G162" s="15"/>
-      <c r="H162" s="15"/>
-      <c r="S162" s="36"/>
-      <c r="U162" s="21"/>
+      <c r="A162"/>
+      <c r="B162"/>
+      <c r="C162"/>
+      <c r="D162"/>
+      <c r="F162" s="35"/>
+      <c r="G162" s="13"/>
+      <c r="H162" s="13"/>
+      <c r="S162" s="32"/>
+      <c r="U162" s="17"/>
     </row>
     <row r="163" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="12"/>
-      <c r="B163" s="12"/>
-      <c r="C163" s="12"/>
-      <c r="D163" s="12"/>
-      <c r="F163" s="39"/>
-      <c r="G163" s="15"/>
-      <c r="H163" s="15"/>
-      <c r="S163" s="36"/>
-      <c r="U163" s="21"/>
+      <c r="A163"/>
+      <c r="B163"/>
+      <c r="C163"/>
+      <c r="D163"/>
+      <c r="F163" s="35"/>
+      <c r="G163" s="13"/>
+      <c r="H163" s="13"/>
+      <c r="S163" s="32"/>
+      <c r="U163" s="17"/>
     </row>
     <row r="164" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="12"/>
-      <c r="B164" s="12"/>
-      <c r="C164" s="12"/>
-      <c r="D164" s="12"/>
-      <c r="F164" s="39"/>
-      <c r="G164" s="15"/>
-      <c r="H164" s="15"/>
-      <c r="S164" s="36"/>
-      <c r="U164" s="21"/>
+      <c r="A164"/>
+      <c r="B164"/>
+      <c r="C164"/>
+      <c r="D164"/>
+      <c r="F164" s="35"/>
+      <c r="G164" s="13"/>
+      <c r="H164" s="13"/>
+      <c r="S164" s="32"/>
+      <c r="U164" s="17"/>
     </row>
     <row r="165" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="12"/>
-      <c r="B165" s="12"/>
-      <c r="C165" s="12"/>
-      <c r="D165" s="12"/>
-      <c r="F165" s="39"/>
-      <c r="G165" s="15"/>
-      <c r="H165" s="15"/>
-      <c r="S165" s="36"/>
-      <c r="U165" s="21"/>
+      <c r="A165"/>
+      <c r="B165"/>
+      <c r="C165"/>
+      <c r="D165"/>
+      <c r="F165" s="35"/>
+      <c r="G165" s="13"/>
+      <c r="H165" s="13"/>
+      <c r="S165" s="32"/>
+      <c r="U165" s="17"/>
     </row>
     <row r="166" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="12"/>
-      <c r="B166" s="12"/>
-      <c r="C166" s="12"/>
-      <c r="D166" s="12"/>
-      <c r="F166" s="39"/>
-      <c r="G166" s="15"/>
-      <c r="H166" s="15"/>
-      <c r="S166" s="36"/>
-      <c r="U166" s="21"/>
+      <c r="A166"/>
+      <c r="B166"/>
+      <c r="C166"/>
+      <c r="D166"/>
+      <c r="F166" s="35"/>
+      <c r="G166" s="13"/>
+      <c r="H166" s="13"/>
+      <c r="S166" s="32"/>
+      <c r="U166" s="17"/>
     </row>
     <row r="167" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="12"/>
-      <c r="B167" s="12"/>
-      <c r="C167" s="12"/>
-      <c r="D167" s="12"/>
-      <c r="F167" s="39"/>
-      <c r="G167" s="15"/>
-      <c r="H167" s="15"/>
-      <c r="S167" s="36"/>
-      <c r="U167" s="21"/>
+      <c r="A167"/>
+      <c r="B167"/>
+      <c r="C167"/>
+      <c r="D167"/>
+      <c r="F167" s="35"/>
+      <c r="G167" s="13"/>
+      <c r="H167" s="13"/>
+      <c r="S167" s="32"/>
+      <c r="U167" s="17"/>
     </row>
     <row r="168" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="12"/>
-      <c r="B168" s="12"/>
-      <c r="C168" s="12"/>
-      <c r="D168" s="12"/>
-      <c r="F168" s="39"/>
-      <c r="G168" s="15"/>
-      <c r="H168" s="15"/>
-      <c r="S168" s="36"/>
-      <c r="U168" s="21"/>
+      <c r="A168"/>
+      <c r="B168"/>
+      <c r="C168"/>
+      <c r="D168"/>
+      <c r="F168" s="35"/>
+      <c r="G168" s="13"/>
+      <c r="H168" s="13"/>
+      <c r="S168" s="32"/>
+      <c r="U168" s="17"/>
     </row>
     <row r="169" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="12"/>
-      <c r="B169" s="12"/>
-      <c r="C169" s="12"/>
-      <c r="D169" s="12"/>
-      <c r="F169" s="39"/>
-      <c r="G169" s="15"/>
-      <c r="H169" s="15"/>
-      <c r="S169" s="36"/>
-      <c r="U169" s="21"/>
+      <c r="A169"/>
+      <c r="B169"/>
+      <c r="C169"/>
+      <c r="D169"/>
+      <c r="F169" s="35"/>
+      <c r="G169" s="13"/>
+      <c r="H169" s="13"/>
+      <c r="S169" s="32"/>
+      <c r="U169" s="17"/>
     </row>
     <row r="170" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="12"/>
-      <c r="B170" s="12"/>
-      <c r="C170" s="12"/>
-      <c r="D170" s="12"/>
-      <c r="F170" s="39"/>
-      <c r="G170" s="15"/>
-      <c r="H170" s="15"/>
-      <c r="S170" s="36"/>
-      <c r="U170" s="21"/>
+      <c r="A170"/>
+      <c r="B170"/>
+      <c r="C170"/>
+      <c r="D170"/>
+      <c r="F170" s="35"/>
+      <c r="G170" s="13"/>
+      <c r="H170" s="13"/>
+      <c r="S170" s="32"/>
+      <c r="U170" s="17"/>
     </row>
     <row r="171" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="12"/>
-      <c r="B171" s="12"/>
-      <c r="C171" s="12"/>
-      <c r="D171" s="12"/>
-      <c r="F171" s="39"/>
-      <c r="G171" s="15"/>
-      <c r="H171" s="15"/>
-      <c r="S171" s="36"/>
-      <c r="U171" s="21"/>
+      <c r="A171"/>
+      <c r="B171"/>
+      <c r="C171"/>
+      <c r="D171"/>
+      <c r="F171" s="35"/>
+      <c r="G171" s="13"/>
+      <c r="H171" s="13"/>
+      <c r="S171" s="32"/>
+      <c r="U171" s="17"/>
     </row>
     <row r="172" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="12"/>
-      <c r="B172" s="12"/>
-      <c r="C172" s="12"/>
-      <c r="D172" s="12"/>
-      <c r="F172" s="39"/>
-      <c r="G172" s="15"/>
-      <c r="H172" s="15"/>
-      <c r="S172" s="36"/>
-      <c r="U172" s="21"/>
+      <c r="A172"/>
+      <c r="B172"/>
+      <c r="C172"/>
+      <c r="D172"/>
+      <c r="F172" s="35"/>
+      <c r="G172" s="13"/>
+      <c r="H172" s="13"/>
+      <c r="S172" s="32"/>
+      <c r="U172" s="17"/>
     </row>
     <row r="173" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="12"/>
-      <c r="B173" s="12"/>
-      <c r="C173" s="12"/>
-      <c r="D173" s="12"/>
-      <c r="F173" s="39"/>
-      <c r="G173" s="15"/>
-      <c r="H173" s="15"/>
-      <c r="S173" s="36"/>
-      <c r="U173" s="21"/>
+      <c r="A173"/>
+      <c r="B173"/>
+      <c r="C173"/>
+      <c r="D173"/>
+      <c r="F173" s="35"/>
+      <c r="G173" s="13"/>
+      <c r="H173" s="13"/>
+      <c r="S173" s="32"/>
+      <c r="U173" s="17"/>
     </row>
     <row r="174" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="12"/>
-      <c r="B174" s="12"/>
-      <c r="C174" s="12"/>
-      <c r="D174" s="12"/>
-      <c r="F174" s="39"/>
-      <c r="G174" s="15"/>
-      <c r="H174" s="15"/>
-      <c r="S174" s="36"/>
-      <c r="U174" s="21"/>
+      <c r="A174"/>
+      <c r="B174"/>
+      <c r="C174"/>
+      <c r="D174"/>
+      <c r="F174" s="35"/>
+      <c r="G174" s="13"/>
+      <c r="H174" s="13"/>
+      <c r="S174" s="32"/>
+      <c r="U174" s="17"/>
     </row>
     <row r="175" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="12"/>
-      <c r="B175" s="12"/>
-      <c r="C175" s="12"/>
-      <c r="D175" s="12"/>
-      <c r="F175" s="39"/>
-      <c r="G175" s="15"/>
-      <c r="H175" s="15"/>
-      <c r="S175" s="36"/>
-      <c r="U175" s="21"/>
+      <c r="A175"/>
+      <c r="B175"/>
+      <c r="C175"/>
+      <c r="D175"/>
+      <c r="F175" s="35"/>
+      <c r="G175" s="13"/>
+      <c r="H175" s="13"/>
+      <c r="S175" s="32"/>
+      <c r="U175" s="17"/>
     </row>
     <row r="176" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="12"/>
-      <c r="B176" s="12"/>
-      <c r="C176" s="12"/>
-      <c r="D176" s="12"/>
-      <c r="F176" s="39"/>
-      <c r="G176" s="15"/>
-      <c r="H176" s="15"/>
-      <c r="S176" s="36"/>
-      <c r="U176" s="21"/>
+      <c r="A176"/>
+      <c r="B176"/>
+      <c r="C176"/>
+      <c r="D176"/>
+      <c r="F176" s="35"/>
+      <c r="G176" s="13"/>
+      <c r="H176" s="13"/>
+      <c r="S176" s="32"/>
+      <c r="U176" s="17"/>
     </row>
     <row r="177" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="12"/>
-      <c r="B177" s="12"/>
-      <c r="C177" s="12"/>
-      <c r="D177" s="12"/>
-      <c r="F177" s="39"/>
-      <c r="G177" s="15"/>
-      <c r="H177" s="15"/>
-      <c r="S177" s="36"/>
-      <c r="U177" s="21"/>
+      <c r="A177"/>
+      <c r="B177"/>
+      <c r="C177"/>
+      <c r="D177"/>
+      <c r="F177" s="35"/>
+      <c r="G177" s="13"/>
+      <c r="H177" s="13"/>
+      <c r="S177" s="32"/>
+      <c r="U177" s="17"/>
     </row>
     <row r="178" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="12"/>
-      <c r="B178" s="12"/>
-      <c r="C178" s="12"/>
-      <c r="D178" s="12"/>
-      <c r="F178" s="39"/>
-      <c r="G178" s="15"/>
-      <c r="H178" s="15"/>
-      <c r="S178" s="36"/>
-      <c r="U178" s="21"/>
+      <c r="A178"/>
+      <c r="B178"/>
+      <c r="C178"/>
+      <c r="D178"/>
+      <c r="F178" s="35"/>
+      <c r="G178" s="13"/>
+      <c r="H178" s="13"/>
+      <c r="S178" s="32"/>
+      <c r="U178" s="17"/>
     </row>
     <row r="179" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="12"/>
-      <c r="B179" s="12"/>
-      <c r="C179" s="12"/>
-      <c r="D179" s="12"/>
-      <c r="F179" s="40"/>
-      <c r="G179" s="16"/>
-      <c r="H179" s="16"/>
-      <c r="S179" s="36"/>
-      <c r="U179" s="21"/>
+      <c r="A179"/>
+      <c r="B179"/>
+      <c r="C179"/>
+      <c r="D179"/>
+      <c r="F179" s="36"/>
+      <c r="G179"/>
+      <c r="H179"/>
+      <c r="S179" s="32"/>
+      <c r="U179" s="17"/>
     </row>
     <row r="180" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="12"/>
-      <c r="B180" s="12"/>
-      <c r="C180" s="12"/>
-      <c r="D180" s="12"/>
-      <c r="F180" s="40"/>
-      <c r="G180" s="16"/>
-      <c r="H180" s="16"/>
-      <c r="S180" s="36"/>
-      <c r="U180" s="21"/>
+      <c r="A180"/>
+      <c r="B180"/>
+      <c r="C180"/>
+      <c r="D180"/>
+      <c r="F180" s="36"/>
+      <c r="G180"/>
+      <c r="H180"/>
+      <c r="S180" s="32"/>
+      <c r="U180" s="17"/>
     </row>
     <row r="181" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="12"/>
-      <c r="B181" s="12"/>
-      <c r="C181" s="12"/>
-      <c r="D181" s="12"/>
-      <c r="F181" s="40"/>
-      <c r="G181" s="16"/>
-      <c r="H181" s="16"/>
-      <c r="S181" s="36"/>
-      <c r="U181" s="21"/>
+      <c r="A181"/>
+      <c r="B181"/>
+      <c r="C181"/>
+      <c r="D181"/>
+      <c r="F181" s="36"/>
+      <c r="G181"/>
+      <c r="H181"/>
+      <c r="S181" s="32"/>
+      <c r="U181" s="17"/>
     </row>
     <row r="182" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="12"/>
-      <c r="B182" s="12"/>
-      <c r="C182" s="12"/>
-      <c r="D182" s="12"/>
-      <c r="F182" s="40"/>
-      <c r="G182" s="16"/>
-      <c r="H182" s="16"/>
-      <c r="S182" s="36"/>
-      <c r="U182" s="21"/>
+      <c r="A182"/>
+      <c r="B182"/>
+      <c r="C182"/>
+      <c r="D182"/>
+      <c r="F182" s="36"/>
+      <c r="G182"/>
+      <c r="H182"/>
+      <c r="S182" s="32"/>
+      <c r="U182" s="17"/>
     </row>
     <row r="183" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="12"/>
-      <c r="B183" s="12"/>
-      <c r="C183" s="12"/>
-      <c r="D183" s="12"/>
-      <c r="F183" s="40"/>
-      <c r="G183" s="16"/>
-      <c r="H183" s="16"/>
-      <c r="S183" s="36"/>
-      <c r="U183" s="21"/>
+      <c r="A183"/>
+      <c r="B183"/>
+      <c r="C183"/>
+      <c r="D183"/>
+      <c r="F183" s="36"/>
+      <c r="G183"/>
+      <c r="H183"/>
+      <c r="S183" s="32"/>
+      <c r="U183" s="17"/>
     </row>
     <row r="184" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="12"/>
-      <c r="B184" s="12"/>
-      <c r="C184" s="12"/>
-      <c r="D184" s="12"/>
-      <c r="F184" s="40"/>
-      <c r="G184" s="16"/>
-      <c r="H184" s="16"/>
-      <c r="S184" s="36"/>
-      <c r="U184" s="21"/>
+      <c r="A184"/>
+      <c r="B184"/>
+      <c r="C184"/>
+      <c r="D184"/>
+      <c r="F184" s="36"/>
+      <c r="G184"/>
+      <c r="H184"/>
+      <c r="S184" s="32"/>
+      <c r="U184" s="17"/>
     </row>
     <row r="185" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="12"/>
-      <c r="B185" s="12"/>
-      <c r="C185" s="12"/>
-      <c r="D185" s="12"/>
-      <c r="F185" s="40"/>
-      <c r="G185" s="16"/>
-      <c r="H185" s="16"/>
-      <c r="S185" s="36"/>
-      <c r="U185" s="21"/>
+      <c r="A185"/>
+      <c r="B185"/>
+      <c r="C185"/>
+      <c r="D185"/>
+      <c r="F185" s="36"/>
+      <c r="G185"/>
+      <c r="H185"/>
+      <c r="S185" s="32"/>
+      <c r="U185" s="17"/>
     </row>
     <row r="186" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="12"/>
-      <c r="B186" s="12"/>
-      <c r="C186" s="12"/>
-      <c r="D186" s="12"/>
-      <c r="F186" s="40"/>
-      <c r="G186" s="16"/>
-      <c r="H186" s="16"/>
-      <c r="S186" s="36"/>
-      <c r="U186" s="21"/>
+      <c r="A186"/>
+      <c r="B186"/>
+      <c r="C186"/>
+      <c r="D186"/>
+      <c r="F186" s="36"/>
+      <c r="G186"/>
+      <c r="H186"/>
+      <c r="S186" s="32"/>
+      <c r="U186" s="17"/>
     </row>
     <row r="187" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="12"/>
-      <c r="B187" s="12"/>
-      <c r="C187" s="12"/>
-      <c r="D187" s="12"/>
-      <c r="F187" s="40"/>
-      <c r="G187" s="16"/>
-      <c r="H187" s="16"/>
-      <c r="S187" s="36"/>
-      <c r="U187" s="21"/>
+      <c r="A187"/>
+      <c r="B187"/>
+      <c r="C187"/>
+      <c r="D187"/>
+      <c r="F187" s="36"/>
+      <c r="G187"/>
+      <c r="H187"/>
+      <c r="S187" s="32"/>
+      <c r="U187" s="17"/>
     </row>
     <row r="188" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="12"/>
-      <c r="B188" s="12"/>
-      <c r="C188" s="12"/>
-      <c r="D188" s="12"/>
-      <c r="F188" s="40"/>
-      <c r="G188" s="16"/>
-      <c r="H188" s="16"/>
-      <c r="S188" s="36"/>
-      <c r="U188" s="21"/>
+      <c r="A188"/>
+      <c r="B188"/>
+      <c r="C188"/>
+      <c r="D188"/>
+      <c r="F188" s="36"/>
+      <c r="G188"/>
+      <c r="H188"/>
+      <c r="S188" s="32"/>
+      <c r="U188" s="17"/>
     </row>
     <row r="189" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="12"/>
-      <c r="B189" s="12"/>
-      <c r="C189" s="12"/>
-      <c r="D189" s="12"/>
-      <c r="F189" s="40"/>
-      <c r="G189" s="16"/>
-      <c r="H189" s="16"/>
-      <c r="S189" s="36"/>
-      <c r="U189" s="21"/>
+      <c r="A189"/>
+      <c r="B189"/>
+      <c r="C189"/>
+      <c r="D189"/>
+      <c r="F189" s="36"/>
+      <c r="G189"/>
+      <c r="H189"/>
+      <c r="S189" s="32"/>
+      <c r="U189" s="17"/>
     </row>
     <row r="190" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="12"/>
-      <c r="B190" s="12"/>
-      <c r="C190" s="12"/>
-      <c r="D190" s="12"/>
-      <c r="F190" s="40"/>
-      <c r="G190" s="16"/>
-      <c r="H190" s="16"/>
-      <c r="S190" s="36"/>
-      <c r="U190" s="21"/>
+      <c r="A190"/>
+      <c r="B190"/>
+      <c r="C190"/>
+      <c r="D190"/>
+      <c r="F190" s="36"/>
+      <c r="G190"/>
+      <c r="H190"/>
+      <c r="S190" s="32"/>
+      <c r="U190" s="17"/>
     </row>
     <row r="191" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="12"/>
-      <c r="B191" s="12"/>
-      <c r="C191" s="12"/>
-      <c r="D191" s="12"/>
-      <c r="F191" s="40"/>
-      <c r="G191" s="16"/>
-      <c r="H191" s="16"/>
-      <c r="S191" s="36"/>
-      <c r="U191" s="21"/>
+      <c r="A191"/>
+      <c r="B191"/>
+      <c r="C191"/>
+      <c r="D191"/>
+      <c r="F191" s="36"/>
+      <c r="G191"/>
+      <c r="H191"/>
+      <c r="S191" s="32"/>
+      <c r="U191" s="17"/>
     </row>
     <row r="192" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="12"/>
-      <c r="B192" s="12"/>
-      <c r="C192" s="12"/>
-      <c r="D192" s="12"/>
-      <c r="F192" s="40"/>
-      <c r="G192" s="16"/>
-      <c r="H192" s="16"/>
-      <c r="S192" s="36"/>
-      <c r="U192" s="21"/>
+      <c r="A192"/>
+      <c r="B192"/>
+      <c r="C192"/>
+      <c r="D192"/>
+      <c r="F192" s="36"/>
+      <c r="G192"/>
+      <c r="H192"/>
+      <c r="S192" s="32"/>
+      <c r="U192" s="17"/>
     </row>
     <row r="193" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="12"/>
-      <c r="B193" s="12"/>
-      <c r="C193" s="12"/>
-      <c r="D193" s="12"/>
-      <c r="F193" s="40"/>
-      <c r="G193" s="16"/>
-      <c r="H193" s="16"/>
-      <c r="S193" s="36"/>
-      <c r="U193" s="21"/>
+      <c r="A193"/>
+      <c r="B193"/>
+      <c r="C193"/>
+      <c r="D193"/>
+      <c r="F193" s="36"/>
+      <c r="G193"/>
+      <c r="H193"/>
+      <c r="S193" s="32"/>
+      <c r="U193" s="17"/>
     </row>
     <row r="194" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="12"/>
-      <c r="B194" s="12"/>
-      <c r="C194" s="12"/>
-      <c r="D194" s="12"/>
-      <c r="F194" s="39"/>
-      <c r="G194" s="15"/>
-      <c r="H194" s="15"/>
-      <c r="S194" s="36"/>
-      <c r="U194" s="21"/>
+      <c r="A194"/>
+      <c r="B194"/>
+      <c r="C194"/>
+      <c r="D194"/>
+      <c r="F194" s="35"/>
+      <c r="G194" s="13"/>
+      <c r="H194" s="13"/>
+      <c r="S194" s="32"/>
+      <c r="U194" s="17"/>
     </row>
     <row r="195" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="12"/>
-      <c r="B195" s="12"/>
-      <c r="C195" s="12"/>
-      <c r="D195" s="12"/>
-      <c r="F195" s="39"/>
-      <c r="G195" s="15"/>
-      <c r="H195" s="15"/>
-      <c r="S195" s="36"/>
-      <c r="U195" s="21"/>
+      <c r="A195"/>
+      <c r="B195"/>
+      <c r="C195"/>
+      <c r="D195"/>
+      <c r="F195" s="35"/>
+      <c r="G195" s="13"/>
+      <c r="H195" s="13"/>
+      <c r="S195" s="32"/>
+      <c r="U195" s="17"/>
     </row>
     <row r="196" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="12"/>
-      <c r="B196" s="12"/>
-      <c r="C196" s="12"/>
-      <c r="D196" s="12"/>
-      <c r="F196" s="39"/>
-      <c r="G196" s="15"/>
-      <c r="H196" s="15"/>
-      <c r="S196" s="36"/>
-      <c r="U196" s="21"/>
+      <c r="A196"/>
+      <c r="B196"/>
+      <c r="C196"/>
+      <c r="D196"/>
+      <c r="F196" s="35"/>
+      <c r="G196" s="13"/>
+      <c r="H196" s="13"/>
+      <c r="S196" s="32"/>
+      <c r="U196" s="17"/>
     </row>
     <row r="197" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="12"/>
-      <c r="B197" s="12"/>
-      <c r="C197" s="12"/>
-      <c r="D197" s="12"/>
-      <c r="F197" s="39"/>
-      <c r="G197" s="15"/>
-      <c r="H197" s="15"/>
-      <c r="S197" s="36"/>
-      <c r="U197" s="21"/>
+      <c r="A197"/>
+      <c r="B197"/>
+      <c r="C197"/>
+      <c r="D197"/>
+      <c r="F197" s="35"/>
+      <c r="G197" s="13"/>
+      <c r="H197" s="13"/>
+      <c r="S197" s="32"/>
+      <c r="U197" s="17"/>
     </row>
     <row r="198" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="12"/>
-      <c r="B198" s="12"/>
-      <c r="C198" s="12"/>
-      <c r="D198" s="12"/>
-      <c r="F198" s="39"/>
-      <c r="G198" s="15"/>
-      <c r="H198" s="15"/>
-      <c r="S198" s="36"/>
-      <c r="U198" s="21"/>
+      <c r="A198"/>
+      <c r="B198"/>
+      <c r="C198"/>
+      <c r="D198"/>
+      <c r="F198" s="35"/>
+      <c r="G198" s="13"/>
+      <c r="H198" s="13"/>
+      <c r="S198" s="32"/>
+      <c r="U198" s="17"/>
     </row>
     <row r="199" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="12"/>
-      <c r="B199" s="12"/>
-      <c r="C199" s="12"/>
-      <c r="D199" s="12"/>
-      <c r="F199" s="39"/>
-      <c r="G199" s="15"/>
-      <c r="H199" s="15"/>
-      <c r="S199" s="36"/>
-      <c r="U199" s="21"/>
+      <c r="A199"/>
+      <c r="B199"/>
+      <c r="C199"/>
+      <c r="D199"/>
+      <c r="F199" s="35"/>
+      <c r="G199" s="13"/>
+      <c r="H199" s="13"/>
+      <c r="S199" s="32"/>
+      <c r="U199" s="17"/>
     </row>
     <row r="200" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="12"/>
-      <c r="B200" s="12"/>
-      <c r="C200" s="12"/>
-      <c r="D200" s="12"/>
-      <c r="F200" s="39"/>
-      <c r="G200" s="15"/>
-      <c r="H200" s="15"/>
-      <c r="S200" s="36"/>
-      <c r="U200" s="21"/>
+      <c r="A200"/>
+      <c r="B200"/>
+      <c r="C200"/>
+      <c r="D200"/>
+      <c r="F200" s="35"/>
+      <c r="G200" s="13"/>
+      <c r="H200" s="13"/>
+      <c r="S200" s="32"/>
+      <c r="U200" s="17"/>
     </row>
     <row r="201" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="12"/>
-      <c r="B201" s="12"/>
-      <c r="C201" s="12"/>
-      <c r="D201" s="12"/>
-      <c r="F201" s="39"/>
-      <c r="G201" s="15"/>
-      <c r="H201" s="15"/>
-      <c r="S201" s="36"/>
-      <c r="U201" s="21"/>
+      <c r="A201"/>
+      <c r="B201"/>
+      <c r="C201"/>
+      <c r="D201"/>
+      <c r="F201" s="35"/>
+      <c r="G201" s="13"/>
+      <c r="H201" s="13"/>
+      <c r="S201" s="32"/>
+      <c r="U201" s="17"/>
     </row>
     <row r="202" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="12"/>
-      <c r="B202" s="12"/>
-      <c r="C202" s="12"/>
-      <c r="D202" s="12"/>
-      <c r="F202" s="39"/>
-      <c r="G202" s="15"/>
-      <c r="H202" s="15"/>
-      <c r="S202" s="36"/>
-      <c r="U202" s="21"/>
+      <c r="A202"/>
+      <c r="B202"/>
+      <c r="C202"/>
+      <c r="D202"/>
+      <c r="F202" s="35"/>
+      <c r="G202" s="13"/>
+      <c r="H202" s="13"/>
+      <c r="S202" s="32"/>
+      <c r="U202" s="17"/>
     </row>
     <row r="203" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="12"/>
-      <c r="B203" s="12"/>
-      <c r="C203" s="12"/>
-      <c r="D203" s="12"/>
-      <c r="F203" s="39"/>
-      <c r="G203" s="15"/>
-      <c r="H203" s="15"/>
-      <c r="S203" s="36"/>
-      <c r="U203" s="21"/>
+      <c r="A203"/>
+      <c r="B203"/>
+      <c r="C203"/>
+      <c r="D203"/>
+      <c r="F203" s="35"/>
+      <c r="G203" s="13"/>
+      <c r="H203" s="13"/>
+      <c r="S203" s="32"/>
+      <c r="U203" s="17"/>
     </row>
     <row r="204" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="12"/>
-      <c r="B204" s="12"/>
-      <c r="C204" s="12"/>
-      <c r="D204" s="12"/>
-      <c r="F204" s="39"/>
-      <c r="G204" s="15"/>
-      <c r="H204" s="15"/>
-      <c r="S204" s="36"/>
-      <c r="U204" s="21"/>
+      <c r="A204"/>
+      <c r="B204"/>
+      <c r="C204"/>
+      <c r="D204"/>
+      <c r="F204" s="35"/>
+      <c r="G204" s="13"/>
+      <c r="H204" s="13"/>
+      <c r="S204" s="32"/>
+      <c r="U204" s="17"/>
     </row>
     <row r="205" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="12"/>
-      <c r="B205" s="12"/>
-      <c r="C205" s="12"/>
-      <c r="D205" s="12"/>
-      <c r="F205" s="39"/>
-      <c r="G205" s="15"/>
-      <c r="H205" s="15"/>
-      <c r="S205" s="36"/>
-      <c r="U205" s="21"/>
+      <c r="A205"/>
+      <c r="B205"/>
+      <c r="C205"/>
+      <c r="D205"/>
+      <c r="F205" s="35"/>
+      <c r="G205" s="13"/>
+      <c r="H205" s="13"/>
+      <c r="S205" s="32"/>
+      <c r="U205" s="17"/>
     </row>
     <row r="206" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="12"/>
-      <c r="B206" s="12"/>
-      <c r="C206" s="12"/>
-      <c r="D206" s="12"/>
-      <c r="F206" s="39"/>
-      <c r="G206" s="15"/>
-      <c r="H206" s="15"/>
-      <c r="S206" s="36"/>
-      <c r="U206" s="21"/>
+      <c r="A206"/>
+      <c r="B206"/>
+      <c r="C206"/>
+      <c r="D206"/>
+      <c r="F206" s="35"/>
+      <c r="G206" s="13"/>
+      <c r="H206" s="13"/>
+      <c r="S206" s="32"/>
+      <c r="U206" s="17"/>
     </row>
     <row r="207" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="12"/>
-      <c r="B207" s="12"/>
-      <c r="C207" s="12"/>
-      <c r="D207" s="12"/>
-      <c r="F207" s="40"/>
-      <c r="G207" s="16"/>
-      <c r="H207" s="16"/>
-      <c r="S207" s="36"/>
-      <c r="U207" s="21"/>
+      <c r="A207"/>
+      <c r="B207"/>
+      <c r="C207"/>
+      <c r="D207"/>
+      <c r="F207" s="36"/>
+      <c r="G207"/>
+      <c r="H207"/>
+      <c r="S207" s="32"/>
+      <c r="U207" s="17"/>
     </row>
     <row r="208" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="12"/>
-      <c r="B208" s="12"/>
-      <c r="C208" s="12"/>
-      <c r="D208" s="12"/>
-      <c r="F208" s="40"/>
-      <c r="G208" s="16"/>
-      <c r="H208" s="16"/>
-      <c r="S208" s="36"/>
-      <c r="U208" s="21"/>
+      <c r="A208"/>
+      <c r="B208"/>
+      <c r="C208"/>
+      <c r="D208"/>
+      <c r="F208" s="36"/>
+      <c r="G208"/>
+      <c r="H208"/>
+      <c r="S208" s="32"/>
+      <c r="U208" s="17"/>
     </row>
     <row r="209" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="12"/>
-      <c r="B209" s="12"/>
-      <c r="C209" s="12"/>
-      <c r="D209" s="12"/>
-      <c r="F209" s="40"/>
-      <c r="G209" s="16"/>
-      <c r="H209" s="16"/>
-      <c r="S209" s="36"/>
-      <c r="U209" s="21"/>
+      <c r="A209"/>
+      <c r="B209"/>
+      <c r="C209"/>
+      <c r="D209"/>
+      <c r="F209" s="36"/>
+      <c r="G209"/>
+      <c r="H209"/>
+      <c r="S209" s="32"/>
+      <c r="U209" s="17"/>
     </row>
     <row r="210" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="12"/>
-      <c r="B210" s="12"/>
-      <c r="C210" s="12"/>
-      <c r="D210" s="12"/>
-      <c r="F210" s="40"/>
-      <c r="G210" s="16"/>
-      <c r="H210" s="16"/>
-      <c r="S210" s="36"/>
-      <c r="U210" s="21"/>
+      <c r="A210"/>
+      <c r="B210"/>
+      <c r="C210"/>
+      <c r="D210"/>
+      <c r="F210" s="36"/>
+      <c r="G210"/>
+      <c r="H210"/>
+      <c r="S210" s="32"/>
+      <c r="U210" s="17"/>
     </row>
     <row r="211" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="12"/>
-      <c r="B211" s="12"/>
-      <c r="C211" s="12"/>
-      <c r="D211" s="12"/>
-      <c r="F211" s="40"/>
-      <c r="G211" s="16"/>
-      <c r="H211" s="16"/>
-      <c r="S211" s="36"/>
-      <c r="U211" s="21"/>
+      <c r="A211"/>
+      <c r="B211"/>
+      <c r="C211"/>
+      <c r="D211"/>
+      <c r="F211" s="36"/>
+      <c r="G211"/>
+      <c r="H211"/>
+      <c r="S211" s="32"/>
+      <c r="U211" s="17"/>
     </row>
     <row r="212" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="12"/>
-      <c r="B212" s="12"/>
-      <c r="C212" s="12"/>
-      <c r="D212" s="12"/>
-      <c r="F212" s="40"/>
-      <c r="G212" s="16"/>
-      <c r="H212" s="16"/>
-      <c r="S212" s="36"/>
-      <c r="U212" s="21"/>
+      <c r="A212"/>
+      <c r="B212"/>
+      <c r="C212"/>
+      <c r="D212"/>
+      <c r="F212" s="36"/>
+      <c r="G212"/>
+      <c r="H212"/>
+      <c r="S212" s="32"/>
+      <c r="U212" s="17"/>
     </row>
     <row r="213" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="12"/>
-      <c r="B213" s="12"/>
-      <c r="C213" s="12"/>
-      <c r="D213" s="12"/>
-      <c r="F213" s="40"/>
-      <c r="G213" s="16"/>
-      <c r="H213" s="16"/>
-      <c r="S213" s="36"/>
-      <c r="U213" s="21"/>
+      <c r="A213"/>
+      <c r="B213"/>
+      <c r="C213"/>
+      <c r="D213"/>
+      <c r="F213" s="36"/>
+      <c r="G213"/>
+      <c r="H213"/>
+      <c r="S213" s="32"/>
+      <c r="U213" s="17"/>
     </row>
     <row r="214" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="12"/>
-      <c r="B214" s="12"/>
-      <c r="C214" s="12"/>
-      <c r="D214" s="12"/>
-      <c r="F214" s="40"/>
-      <c r="G214" s="16"/>
-      <c r="H214" s="16"/>
-      <c r="S214" s="36"/>
-      <c r="U214" s="21"/>
+      <c r="A214"/>
+      <c r="B214"/>
+      <c r="C214"/>
+      <c r="D214"/>
+      <c r="F214" s="36"/>
+      <c r="G214"/>
+      <c r="H214"/>
+      <c r="S214" s="32"/>
+      <c r="U214" s="17"/>
     </row>
     <row r="215" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215"/>
       <c r="B215"/>
       <c r="C215"/>
       <c r="D215"/>
-      <c r="F215" s="42"/>
-      <c r="G215" s="14"/>
-      <c r="H215" s="14"/>
-      <c r="S215" s="36"/>
-      <c r="U215" s="21"/>
+      <c r="F215" s="36"/>
+      <c r="G215"/>
+      <c r="H215"/>
+      <c r="S215" s="32"/>
+      <c r="U215" s="17"/>
     </row>
     <row r="216" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216"/>
       <c r="B216"/>
       <c r="C216"/>
       <c r="D216"/>
-      <c r="F216" s="42"/>
-      <c r="G216" s="14"/>
-      <c r="H216" s="14"/>
-      <c r="S216" s="36"/>
-      <c r="U216" s="21"/>
+      <c r="F216" s="36"/>
+      <c r="G216"/>
+      <c r="H216"/>
+      <c r="S216" s="32"/>
+      <c r="U216" s="17"/>
     </row>
     <row r="217" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217"/>
       <c r="B217"/>
       <c r="C217"/>
       <c r="D217"/>
-      <c r="F217" s="42"/>
-      <c r="G217" s="14"/>
-      <c r="H217" s="14"/>
-      <c r="S217" s="36"/>
-      <c r="U217" s="21"/>
+      <c r="F217" s="36"/>
+      <c r="G217"/>
+      <c r="H217"/>
+      <c r="S217" s="32"/>
+      <c r="U217" s="17"/>
     </row>
     <row r="218" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218"/>
       <c r="B218"/>
       <c r="C218"/>
       <c r="D218"/>
-      <c r="F218" s="42"/>
-      <c r="G218" s="14"/>
-      <c r="H218" s="14"/>
-      <c r="S218" s="36"/>
-      <c r="U218" s="21"/>
+      <c r="F218" s="36"/>
+      <c r="G218"/>
+      <c r="H218"/>
+      <c r="S218" s="32"/>
+      <c r="U218" s="17"/>
     </row>
     <row r="219" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219"/>
       <c r="B219"/>
       <c r="C219"/>
       <c r="D219"/>
-      <c r="F219" s="42"/>
-      <c r="G219" s="14"/>
-      <c r="H219" s="14"/>
-      <c r="S219" s="36"/>
-      <c r="U219" s="21"/>
+      <c r="F219" s="36"/>
+      <c r="G219"/>
+      <c r="H219"/>
+      <c r="S219" s="32"/>
+      <c r="U219" s="17"/>
     </row>
     <row r="220" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220"/>
       <c r="B220"/>
       <c r="C220"/>
       <c r="D220"/>
-      <c r="F220" s="42"/>
-      <c r="G220" s="14"/>
-      <c r="H220" s="14"/>
-      <c r="S220" s="36"/>
-      <c r="U220" s="21"/>
+      <c r="F220" s="36"/>
+      <c r="G220"/>
+      <c r="H220"/>
+      <c r="S220" s="32"/>
+      <c r="U220" s="17"/>
     </row>
     <row r="221" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221"/>
       <c r="B221"/>
       <c r="C221"/>
       <c r="D221"/>
-      <c r="F221" s="42"/>
-      <c r="G221" s="14"/>
-      <c r="H221" s="14"/>
-      <c r="S221" s="36"/>
-      <c r="U221" s="21"/>
+      <c r="F221" s="36"/>
+      <c r="G221"/>
+      <c r="H221"/>
+      <c r="S221" s="32"/>
+      <c r="U221" s="17"/>
     </row>
     <row r="222" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222"/>
       <c r="B222"/>
       <c r="C222"/>
       <c r="D222"/>
-      <c r="F222" s="42"/>
-      <c r="G222" s="14"/>
-      <c r="H222" s="14"/>
-      <c r="S222" s="36"/>
-      <c r="U222" s="21"/>
+      <c r="F222" s="36"/>
+      <c r="G222"/>
+      <c r="H222"/>
+      <c r="S222" s="32"/>
+      <c r="U222" s="17"/>
     </row>
     <row r="223" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223"/>
       <c r="B223"/>
       <c r="C223"/>
       <c r="D223"/>
-      <c r="F223" s="42"/>
-      <c r="G223" s="14"/>
-      <c r="H223" s="14"/>
-      <c r="S223" s="36"/>
-      <c r="U223" s="21"/>
+      <c r="F223" s="36"/>
+      <c r="G223"/>
+      <c r="H223"/>
+      <c r="S223" s="32"/>
+      <c r="U223" s="17"/>
     </row>
     <row r="224" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F224" s="43"/>
-      <c r="G224" s="17"/>
-      <c r="H224" s="17"/>
-      <c r="S224" s="36"/>
-      <c r="U224" s="21"/>
+      <c r="F224" s="38"/>
+      <c r="S224" s="32"/>
+      <c r="U224" s="17"/>
     </row>
     <row r="225" spans="6:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F225" s="43"/>
-      <c r="G225" s="17"/>
-      <c r="H225" s="17"/>
-      <c r="S225" s="36"/>
-      <c r="U225" s="21"/>
+      <c r="F225" s="38"/>
+      <c r="S225" s="32"/>
+      <c r="U225" s="17"/>
     </row>
     <row r="226" spans="6:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F226" s="43"/>
-      <c r="G226" s="17"/>
-      <c r="H226" s="17"/>
-      <c r="S226" s="36"/>
-      <c r="U226" s="21"/>
+      <c r="F226" s="38"/>
+      <c r="S226" s="32"/>
+      <c r="U226" s="17"/>
     </row>
     <row r="227" spans="6:21" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="F227" s="43"/>
-      <c r="G227" s="17"/>
-      <c r="H227" s="17"/>
-      <c r="S227" s="36"/>
-      <c r="U227" s="21"/>
+      <c r="F227" s="38"/>
+      <c r="S227" s="32"/>
+      <c r="U227" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V130" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="17">
-      <filters>
-        <filter val="JA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:V130" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U199">
     <sortCondition ref="A1:A199"/>
   </sortState>
@@ -8441,7 +8627,7 @@
       <c r="A2" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="37">
+      <c r="B2" s="33">
         <v>46076</v>
       </c>
       <c r="C2" t="s">
@@ -8478,10 +8664,10 @@
       <c r="E1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="14" t="s">
         <v>21</v>
       </c>
       <c r="I1" t="s">
@@ -8920,6 +9106,27 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="8a0b3f22-905c-486c-9de8-ccf2a7293986">QYYV7MT4TVFT-2009251345-26767</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="8a0b3f22-905c-486c-9de8-ccf2a7293986">
+      <Url>https://dataportal.uu.se/project/swedigarch_m3/_layouts/15/DocIdRedir.aspx?ID=QYYV7MT4TVFT-2009251345-26767</Url>
+      <Description>QYYV7MT4TVFT-2009251345-26767</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010066F6F36516100E468A61A2DAA3D1CCC6" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="095cfb88db7bb5d0ccb90daefb459dfb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8a0b3f22-905c-486c-9de8-ccf2a7293986" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af8711ea2a5849a91fdbd5169f57417d" ns2:_="">
     <xsd:import namespace="8a0b3f22-905c-486c-9de8-ccf2a7293986"/>
@@ -9064,27 +9271,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="8a0b3f22-905c-486c-9de8-ccf2a7293986">QYYV7MT4TVFT-2009251345-26767</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="8a0b3f22-905c-486c-9de8-ccf2a7293986">
-      <Url>https://dataportal.uu.se/project/swedigarch_m3/_layouts/15/DocIdRedir.aspx?ID=QYYV7MT4TVFT-2009251345-26767</Url>
-      <Description>QYYV7MT4TVFT-2009251345-26767</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A785EF3D-3801-4F50-8E61-4EBD9AE391E3}">
   <ds:schemaRefs>
@@ -9094,19 +9280,9 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAF48AFB-3A15-4398-847D-CB0D10FA4E97}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8D150A3-0B5F-4415-B9F3-6952530BD6AA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8a0b3f22-905c-486c-9de8-ccf2a7293986"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9128,9 +9304,19 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8D150A3-0B5F-4415-B9F3-6952530BD6AA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAF48AFB-3A15-4398-847D-CB0D10FA4E97}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8a0b3f22-905c-486c-9de8-ccf2a7293986"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>